--- a/workspaces/btc_daily_14days/ma/ma_ratio_7.xlsx
+++ b/workspaces/btc_daily_14days/ma/ma_ratio_7.xlsx
@@ -575,46 +575,46 @@
         <v>21</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-4.874390701166689</v>
+        <v>-4.859772930135072</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-11.25060083801623</v>
+        <v>-11.21508793219144</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-6.884076616639881</v>
+        <v>-6.862993243182579</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-1.989975650621759</v>
+        <v>-1.98434004484082</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-7.296020471796439</v>
+        <v>-7.273207523815358</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-11.7679197912012</v>
+        <v>-11.73033454525561</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-2.317804766376106</v>
+        <v>-2.310402034379898</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1.98383552014586</v>
+        <v>1.977331289834439</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-7.619497855555792</v>
+        <v>-7.59508761280577</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-3.700723365681313</v>
+        <v>-3.689129135341432</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-8.680609745973321</v>
+        <v>-8.652978156377294</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-13.42297468097318</v>
+        <v>-13.38031293627258</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-4.295812097318752</v>
+        <v>-4.282280474702247</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.7307286549445209</v>
+        <v>0.7283047254303696</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>26</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>12.89117706440716</v>
+        <v>12.84899529283389</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>7.435295421849681</v>
+        <v>7.411299806509028</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3.194117827582915</v>
+        <v>3.183127789785381</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-8.22170849913843</v>
+        <v>-8.196024200580801</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-12.61270302551655</v>
+        <v>-12.57257653985441</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-4.616409929128594</v>
+        <v>-4.601321753149655</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-12.40603523064058</v>
+        <v>-12.36619665146949</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-9.024142226926308</v>
+        <v>-8.995422477986828</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-5.234012207248369</v>
+        <v>-5.216968523947685</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-13.79648939668949</v>
+        <v>-13.75238656071738</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-10.14968138993359</v>
+        <v>-10.11701856795491</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-13.97433979407093</v>
+        <v>-13.92941538324592</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-14.39912318124805</v>
+        <v>-14.35303629707123</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-6.435079049201079</v>
+        <v>-6.414552417424602</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>27</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-4.34529017206183</v>
+        <v>-4.332384176024462</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1.45092767101211</v>
+        <v>1.445935038821951</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-13.76584999921921</v>
+        <v>-13.72223434798149</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-6.225997765459063</v>
+        <v>-6.206418004204458</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-3.059216544296817</v>
+        <v>-3.049402604082786</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-6.470640405028618</v>
+        <v>-6.44936780652025</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-6.557106815672327</v>
+        <v>-6.535625481275005</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-10.73672439140861</v>
+        <v>-10.7020980830337</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-7.089688567958021</v>
+        <v>-7.066430057763426</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-4.231354441607813</v>
+        <v>-4.217549421407909</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-4.437822463433378</v>
+        <v>-4.423168838492913</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>3.023156577174788</v>
+        <v>3.01380076474512</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>2.60254690636836</v>
+        <v>2.594355393157819</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-4.577500699445004</v>
+        <v>-4.562700565574431</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>48</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.486339342106781</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-12.44144540220203</v>
+        <v>-12.40114363817775</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-4.502060878004798</v>
+        <v>-4.487889329487722</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-6.457739137515638</v>
+        <v>-6.437033183768314</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.7421293310609158</v>
+        <v>-0.7397006857090105</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-2.53065846763355</v>
+        <v>-2.521857424870831</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-8.875604608979394</v>
+        <v>-8.846143487851073</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.9977204004505396</v>
+        <v>-0.9942602340128417</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-1.059315433865081</v>
+        <v>-1.055320673980063</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-3.999528744963108</v>
+        <v>-3.986220924445014</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-6.294553105903148</v>
+        <v>-6.273557053160332</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-8.350730063873257</v>
+        <v>-8.323102000855798</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-10.86384889763901</v>
+        <v>-10.82819804292811</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-12.70618918369784</v>
+        <v>-12.66455241742365</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>47</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4.953370190429297</v>
+        <v>4.936020005836113</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>5.470836628938365</v>
+        <v>5.452890427849809</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2.948484654107624</v>
+        <v>2.938365563048599</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>13.72598471749199</v>
+        <v>13.68045940356172</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>8.930813408182004</v>
+        <v>8.901319994962485</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2.83956379378678</v>
+        <v>2.830822417848204</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>4.886201322534482</v>
+        <v>4.870874887555921</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>6.551134535419877</v>
+        <v>6.529720236357086</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>6.491448858771456</v>
+        <v>6.470575756599573</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>5.641109553703814</v>
+        <v>5.622864969607853</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>7.570104996422948</v>
+        <v>7.545768920396107</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>5.472838350535426</v>
+        <v>5.455430369961206</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.918553025384121</v>
+        <v>2.909497777906878</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>1.035044695103601</v>
+        <v>1.032256093213704</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>58</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>6.127251334962047</v>
+        <v>6.105491696508281</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2.792266261703688</v>
+        <v>2.782822142096315</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>11.02312835128639</v>
+        <v>10.98563887493374</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>9.430940476814271</v>
+        <v>9.398594155441153</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>8.894337924476318</v>
+        <v>8.864167529559296</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>5.741419290261966</v>
+        <v>5.722703219968629</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>10.83838500515262</v>
+        <v>10.80266939527981</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>8.646208478257321</v>
+        <v>8.61718332151186</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>3.403983233957163</v>
+        <v>3.392905014952021</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-4.359771679789233</v>
+        <v>-4.344950756731635</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.6194350276778451</v>
+        <v>0.617763748143723</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.6539787746203771</v>
+        <v>0.6522696418838407</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-6.685437575148711</v>
+        <v>-6.66251009758043</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-9.89664762726543</v>
+        <v>-9.86282827949357</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>72</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.673228346456057</v>
+        <v>1.665954122481203</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-5.495329310391398</v>
+        <v>-5.476758962116214</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-7.281322450220294</v>
+        <v>-7.2575062378571</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-5.762785365844913</v>
+        <v>-5.744286496745332</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-3.522622828285982</v>
+        <v>-3.511368094733001</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>3.727522701924904</v>
+        <v>3.71505270383399</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-3.311734392105357</v>
+        <v>-3.300288370500937</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-7.954702894729458</v>
+        <v>-7.927957778599122</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-9.410102817205633</v>
+        <v>-9.377745226057776</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-8.872721167788541</v>
+        <v>-8.84196256368439</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-9.08036287272418</v>
+        <v>-9.04892523422545</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-9.048372257213593</v>
+        <v>-9.016965036410213</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-6.686163511113833</v>
+        <v>-6.662449602916688</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-9.225009411043104</v>
+        <v>-9.192330195202381</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>83</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>6.542706258103557</v>
+        <v>6.518107291571617</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>7.34273519524654</v>
+        <v>7.317203248660405</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>3.333336259942449</v>
+        <v>3.321040869638772</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>3.4646944195812</v>
+        <v>3.451709042243287</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>5.338838823482327</v>
+        <v>5.319586830020384</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>3.225039000322987</v>
+        <v>3.213805742865617</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.7273597106395968</v>
+        <v>0.7251638688439712</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.2596226384244318</v>
+        <v>0.2587687389775581</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1.405505595772759</v>
+        <v>1.401405138319745</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-4.277481475582547</v>
+        <v>-4.261503869693492</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-3.27593729961896</v>
+        <v>-3.263479144443643</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-2.03408787257785</v>
+        <v>-2.02589054093081</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.456560811500744</v>
+        <v>-2.446643402180463</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.9981493761952009</v>
+        <v>-0.9928656704366503</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>121</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-2.906661460706033</v>
+        <v>-2.898513459151374</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.212752444217202</v>
+        <v>-1.208820015536809</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>7.487898656488369</v>
+        <v>7.459895214273644</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3.484795451139945</v>
+        <v>3.471001199319787</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>6.256255542354118</v>
+        <v>6.232597260950477</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>5.728015463592598</v>
+        <v>5.707101750731205</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.150278572813896</v>
+        <v>-0.1494279037820263</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.037823076872833</v>
+        <v>1.034109032571443</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>4.289687729204203</v>
+        <v>4.274933891802888</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>3.438094339538608</v>
+        <v>3.427100557435338</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.576196468760401</v>
+        <v>1.571829644688044</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.704887618224305</v>
+        <v>-1.697414952406255</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.4689712377497273</v>
+        <v>-0.4656729259727399</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1.439912977763889</v>
+        <v>1.436687251996879</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>149</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.829008790008629</v>
+        <v>-2.820515622986036</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.9288398703198695</v>
+        <v>0.9250080356351091</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-4.166422772375384</v>
+        <v>-4.152690856753892</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.6649092419688571</v>
+        <v>0.6606638659758204</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.5456718599131207</v>
+        <v>-0.5455443134675377</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.2481809145286746</v>
+        <v>-0.2482062973108015</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>5.717127853756644</v>
+        <v>5.695929638211616</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.215832736293166</v>
+        <v>1.211156987864747</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1.154833848671657</v>
+        <v>1.150740946135187</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.3022139272821818</v>
+        <v>0.3021792997723907</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>3.46223173938138</v>
+        <v>3.450414204662643</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.215719988488878</v>
+        <v>-1.209506110555708</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.638067239873877</v>
+        <v>-1.630104157958044</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.306543939300184</v>
+        <v>1.30356838794453</v>
       </c>
     </row>
     <row r="16">
@@ -1092,49 +1092,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.897693639358792</v>
+        <v>-0.8983847249216197</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.6824717769179784</v>
+        <v>0.6838135730501165</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.352236908481522</v>
+        <v>1.355068424677789</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.4184607589084095</v>
+        <v>0.4199910523778669</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-2.250608860629896</v>
+        <v>-2.253476881367519</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.5317734576237</v>
+        <v>1.534718511457001</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.9155774761470354</v>
+        <v>0.9173334263898028</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.08229591682275128</v>
+        <v>-0.08230255086295557</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.208902453193659</v>
+        <v>-1.210931130380608</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.4565172368786818</v>
+        <v>-0.4577518784480219</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.4055389764408872</v>
+        <v>0.4058917231571755</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.507718688286239</v>
+        <v>1.5093727306365</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>2.156144515571455</v>
+        <v>2.158765389188069</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2.939687582891857</v>
+        <v>2.943736352628875</v>
       </c>
     </row>
     <row r="17">
@@ -1144,49 +1144,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2.119107805251197</v>
+        <v>2.129569782056713</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.5077637559394574</v>
+        <v>0.5105543624217006</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>4.003587934139212</v>
+        <v>4.021755005860435</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.8113882249803765</v>
+        <v>0.816978419373747</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.1070425745320662</v>
+        <v>0.1091448416735616</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.4028349771993334</v>
+        <v>0.4059291493809241</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.157662494456446</v>
+        <v>-1.161509977801046</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-2.360525842535196</v>
+        <v>-2.369805515337085</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.942476524089841</v>
+        <v>-0.9466863934027714</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.417318500203912</v>
+        <v>-1.424446050920771</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.732025427224094</v>
+        <v>-2.743861142061824</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-3.067514564229484</v>
+        <v>-3.081800032239649</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.746747755046222</v>
+        <v>-2.759842779636621</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.6484464286396943</v>
+        <v>-0.6524706330379857</v>
       </c>
     </row>
     <row r="18">
@@ -1196,49 +1196,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.5646549374205847</v>
+        <v>-0.5642944193313042</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.473806130067608</v>
+        <v>-2.480363654860746</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2.474673806447875</v>
+        <v>2.484495802643444</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3.357955174310653</v>
+        <v>3.369837590796308</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>4.602615459705902</v>
+        <v>4.617473731822827</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2.821429006194059</v>
+        <v>2.830969249247595</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.738776671507537</v>
+        <v>2.747188282532413</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.97692899970292</v>
+        <v>1.98235628090967</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.916800766335427</v>
+        <v>1.921881065806076</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.1766963724923443</v>
+        <v>0.1757624477472177</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.217702913119581</v>
+        <v>-1.22257994270894</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.481373587461668</v>
+        <v>-1.487969614094787</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.902497717297713</v>
+        <v>-1.910334622792618</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-2.971723594109854</v>
+        <v>-2.981716596529083</v>
       </c>
     </row>
     <row r="19">
@@ -1248,49 +1248,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.101638775790839</v>
+        <v>-0.1005236913592356</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.2324546111796053</v>
+        <v>0.2328062723476378</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.214675336342282</v>
+        <v>-2.216381084127569</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.03439420234674628</v>
+        <v>-0.0322288104804187</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.3435647895351082</v>
+        <v>-0.3421629228678853</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.8649529855595759</v>
+        <v>0.8681141136679642</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.4491057852926232</v>
+        <v>0.4508459538186216</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.8974126644258149</v>
+        <v>0.8992730732530845</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.977338320549514</v>
+        <v>1.981065736567047</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.13266760900602</v>
+        <v>1.133775613323373</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.157278662686927</v>
+        <v>1.158211904861957</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.334252568246676</v>
+        <v>2.336633848919554</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.23023107523634</v>
+        <v>1.230463092404321</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.022223895815209</v>
+        <v>1.022518520790506</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>413</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-3.098765196723292</v>
+        <v>-3.091181042625522</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.078377550607591</v>
+        <v>-1.074767644823559</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.473246257204238</v>
+        <v>-1.472043926856259</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-2.795777628228691</v>
+        <v>-2.791240106364114</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.881414339668851</v>
+        <v>-1.879309168532387</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.099710900742565</v>
+        <v>-1.099971405651289</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.9947321374330969</v>
+        <v>0.9891678983198133</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.2857459228254342</v>
+        <v>0.2837783141501617</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.198852060128267</v>
+        <v>-2.192964092311435</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.6274462389003617</v>
+        <v>-0.6239679274276568</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.1055333644470764</v>
+        <v>-0.103335551274867</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.500141607108375</v>
+        <v>-2.489162683826429</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.9810684951380182</v>
+        <v>-0.9742011104756472</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.944382415656342</v>
+        <v>-1.93513353122605</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>319</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.082780012999912</v>
+        <v>-1.079611722804167</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.694353625964233</v>
+        <v>-2.682418276532417</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-3.716181580209692</v>
+        <v>-3.705304676479358</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-3.899408071426649</v>
+        <v>-3.888161204984421</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.831763189990212</v>
+        <v>1.819875054847287</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.502245880056897</v>
+        <v>1.491322466728484</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2.98491028190692</v>
+        <v>2.968540312768212</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>2.519724201532973</v>
+        <v>2.507740291088091</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>3.715695272549006</v>
+        <v>3.700545931624809</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>3.493222818270347</v>
+        <v>3.481736291453508</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>2.032389191374101</v>
+        <v>2.027017007182749</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>2.694006162773938</v>
+        <v>2.689378935734261</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>3.531825478168173</v>
+        <v>3.523814024593783</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>4.412413460882426</v>
+        <v>4.400494604518968</v>
       </c>
     </row>
     <row r="22">
@@ -1404,49 +1404,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-2.666448700832852</v>
+        <v>-2.686595543580594</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.509856223831633</v>
+        <v>-1.528917408601515</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.558704169182583</v>
+        <v>-1.567506350018284</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.428451036575133</v>
+        <v>-1.435644216612879</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-3.696976057875631</v>
+        <v>-3.7125575696396</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-3.053513358914259</v>
+        <v>-3.063662869137829</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-4.868350882414987</v>
+        <v>-4.891715726758513</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.072264116316788</v>
+        <v>-3.088119854194879</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.441510276066758</v>
+        <v>-2.454306336330383</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.25009578137891</v>
+        <v>-2.268341052201002</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-3.643704288594719</v>
+        <v>-3.676003212481533</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.9791729101460476</v>
+        <v>-0.9973291074848376</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.399436782759516</v>
+        <v>-1.41951850494565</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-3.235348083146427</v>
+        <v>-3.267699270571491</v>
       </c>
     </row>
     <row r="23">
@@ -1456,49 +1456,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-2.704408784344992</v>
+        <v>-2.711216683975707</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.3253678136612095</v>
+        <v>0.3229242234940699</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-5.132792032175836</v>
+        <v>-5.143366566618887</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-3.73671611475821</v>
+        <v>-3.744049152040787</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-4.697078258100476</v>
+        <v>-4.704417340132984</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-5.665459105194934</v>
+        <v>-5.674428002932586</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-7.859897463817376</v>
+        <v>-7.874089781105177</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-5.373494364708627</v>
+        <v>-5.383704702967137</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-4.172574112022119</v>
+        <v>-4.180544770258187</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.916451561142786</v>
+        <v>-2.923967035225772</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-3.12331716360508</v>
+        <v>-3.13298966748853</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-3.935465123046782</v>
+        <v>-3.94784301557231</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.995278799864657</v>
+        <v>-2.00325680054835</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-3.43721775827364</v>
+        <v>-3.4484507225093</v>
       </c>
     </row>
     <row r="24">
@@ -1508,49 +1508,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>4.506561679790053</v>
+        <v>4.518514806206738</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.394988066825775</v>
+        <v>1.393665955171691</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-4.499880639770879</v>
+        <v>-4.520369504585929</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-7.369627507163322</v>
+        <v>-7.398884059789864</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-5.408048722235492</v>
+        <v>-5.426519627157518</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-11.11060678451983</v>
+        <v>-11.15009230625973</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-10.19534050179214</v>
+        <v>-10.23460953741326</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-7.162523900573554</v>
+        <v>-7.191177384726331</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-10.23770498713039</v>
+        <v>-10.27732683340279</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-5.795528267048091</v>
+        <v>-5.822392690376809</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-6.496312246536675</v>
+        <v>-6.529658577508457</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-6.45922732457521</v>
+        <v>-6.495275420163026</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-8.382240623234388</v>
+        <v>-8.423067719550104</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-5.628436099932564</v>
+        <v>-5.660783573203496</v>
       </c>
     </row>
     <row r="25">
@@ -1560,49 +1560,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-2.493438320210011</v>
+        <v>-2.51437395265642</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.962154790317086</v>
+        <v>-1.989561436428758</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-3.071309211199356</v>
+        <v>-3.111467560710217</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-6.512484650020461</v>
+        <v>-6.578336730261036</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-7.765191579378353</v>
+        <v>-7.827617828854919</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-2.467749641662728</v>
+        <v>-2.502769245027658</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.123911930363498</v>
+        <v>-1.155315379033119</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-2.305381043430749</v>
+        <v>-2.34097161858967</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.9089265443698906</v>
+        <v>0.8915841269131448</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.791718981244586</v>
+        <v>-2.836238899841391</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-2.269887631957594</v>
+        <v>-2.321567763727323</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.514596243770143</v>
+        <v>-1.567760145950231</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.219619066635659</v>
+        <v>-1.268590296463522</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.687021670026269</v>
+        <v>-1.738293424618846</v>
       </c>
     </row>
     <row r="26">
@@ -2213,10 +2213,8 @@
           <t>X &gt; -0.1018</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4088~4101</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4088</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-0.286659485779353</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; -0.09444</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4067~4080</t>
-        </is>
+      <c r="B7" t="n">
+        <v>4067</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.2630461633472265</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; -0.0871</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>4041~4054</t>
-        </is>
+      <c r="B8" t="n">
+        <v>4041</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-0.347409706495128</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; -0.07977</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>4014~4027</t>
-        </is>
+      <c r="B9" t="n">
+        <v>4014</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.320604945489336</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; -0.07243</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3966~3979</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3966</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.2943933340325415</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; -0.0651</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3919~3932</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3919</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.357120924482615</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; -0.05776</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3861~3874</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3861</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.4542023883565989</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; -0.05043</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3789~3802</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3789</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.4944903980637321</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; -0.04309</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3706~3719</t>
-        </is>
+      <c r="B14" t="n">
+        <v>3706</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.6515453382255671</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; -0.03576</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3585~3598</t>
-        </is>
+      <c r="B15" t="n">
+        <v>3585</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-0.5757062468358711</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; -0.02842</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>3436~3449</t>
-        </is>
+      <c r="B16" t="n">
+        <v>3436</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.4783614863450794</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; -0.02109</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>3249~3261</t>
-        </is>
+      <c r="B17" t="n">
+        <v>3249</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.454186556947171</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; -0.01375</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2980~2990</t>
-        </is>
+      <c r="B18" t="n">
+        <v>2980</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.6874182533203381</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; -0.006416</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2645~2653</t>
-        </is>
+      <c r="B19" t="n">
+        <v>2645</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-0.7030123873038292</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; 0.0009193</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2208~2214</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2208</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-0.8222549417095237</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 0.008254</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1795~1801</t>
-        </is>
+      <c r="B21" t="n">
+        <v>1795</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-0.3002123346464032</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 0.01559</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1476~1482</t>
-        </is>
+      <c r="B22" t="n">
+        <v>1476</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-0.131764905904987</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 0.02292</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1190~1193</t>
-        </is>
+      <c r="B23" t="n">
+        <v>1190</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>0.4822532137380549</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 0.03026</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>954~956</t>
-        </is>
+      <c r="B24" t="n">
+        <v>954</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>1.272252056359065</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 0.0376</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>755~756</t>
-        </is>
+      <c r="B25" t="n">
+        <v>755</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>0.4166145898429292</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 0.04493</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>616~616</t>
-        </is>
+      <c r="B26" t="n">
+        <v>616</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>1.077990251218594</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 0.05227</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>493~493</t>
-        </is>
+      <c r="B27" t="n">
+        <v>493</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>2.273295959708882</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 0.0596</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>402~402</t>
-        </is>
+      <c r="B28" t="n">
+        <v>402</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>3.227954714615898</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 0.06694</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>328~328</t>
-        </is>
+      <c r="B29" t="n">
+        <v>328</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>4.823634850521728</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 0.07427</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>266~266</t>
-        </is>
+      <c r="B30" t="n">
+        <v>266</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>5.777238371519353</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 0.08161</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>201~201</t>
-        </is>
+      <c r="B31" t="n">
+        <v>201</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>2.232929838993996</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 0.08894</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>164~164</t>
-        </is>
+      <c r="B32" t="n">
+        <v>164</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-1.883682222649</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 0.09628</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>130~130</t>
-        </is>
+      <c r="B33" t="n">
+        <v>130</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-4.031899858671515</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 0.1036</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>100~100</t>
-        </is>
+      <c r="B34" t="n">
+        <v>100</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-4.493438320209975</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 0.1109</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B35" t="n">
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-6.064866891638545</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; -0.1018</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>12.98275215598051</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; -0.09444</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>105~105</t>
-        </is>
+      <c r="B7" t="n">
+        <v>105</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>9.41132358455193</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; -0.0871</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>131~131</t>
-        </is>
+      <c r="B8" t="n">
+        <v>131</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>10.10198152711828</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; -0.07977</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>158~158</t>
-        </is>
+      <c r="B9" t="n">
+        <v>158</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>7.633143958271035</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; -0.07243</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>206~206</t>
-        </is>
+      <c r="B10" t="n">
+        <v>206</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>5.273551971052157</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; -0.0651</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>253~253</t>
-        </is>
+      <c r="B11" t="n">
+        <v>253</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>5.214071561212947</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; -0.05776</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>311~311</t>
-        </is>
+      <c r="B12" t="n">
+        <v>311</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>5.384375184613177</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; -0.05043</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>383~383</t>
-        </is>
+      <c r="B13" t="n">
+        <v>383</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>4.686718337753469</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; -0.04309</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>466~466</t>
-        </is>
+      <c r="B14" t="n">
+        <v>466</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>5.017291293523925</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; -0.03576</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>587~587</t>
-        </is>
+      <c r="B15" t="n">
+        <v>587</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>3.38390409887009</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; -0.02842</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>736~736</t>
-        </is>
+      <c r="B16" t="n">
+        <v>736</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>2.126126897181337</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; -0.02109</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>923~924</t>
-        </is>
+      <c r="B17" t="n">
+        <v>923</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>1.510890684119026</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; -0.01375</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1192~1195</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1192</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>1.648821094015972</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; -0.006416</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1527~1532</t>
-        </is>
+      <c r="B19" t="n">
+        <v>1527</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>1.161914160207772</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; 0.0009193</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1964~1971</t>
-        </is>
+      <c r="B20" t="n">
+        <v>1964</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>0.8804835468625711</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 0.008254</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2377~2384</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2377</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>0.1911254381792844</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 0.01559</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2696~2703</t>
-        </is>
+      <c r="B22" t="n">
+        <v>2696</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>0.04078291545410195</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 0.02292</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2982~2992</t>
-        </is>
+      <c r="B23" t="n">
+        <v>2982</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-0.2207110474827019</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 0.03026</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>3218~3229</t>
-        </is>
+      <c r="B24" t="n">
+        <v>3218</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-0.4030078463790687</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 0.0376</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3417~3429</t>
-        </is>
+      <c r="B25" t="n">
+        <v>3417</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-0.1166520851560264</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 0.04493</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3556~3569</t>
-        </is>
+      <c r="B26" t="n">
+        <v>3556</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-0.2098855042951513</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 0.05227</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3679~3692</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3679</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-0.3265910829401975</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 0.0596</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3770~3783</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3770</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-0.3654975324753664</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 0.06694</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3844~3857</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3844</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-0.4322508688228837</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 0.07427</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3906~3919</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3906</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-0.4138261742543747</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 0.08161</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3971~3984</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3971</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-0.1340005692059663</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 0.08894</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>4008~4021</t>
-        </is>
+      <c r="B32" t="n">
+        <v>4008</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>0.05567881483106163</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 0.09628</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>4042~4055</t>
-        </is>
+      <c r="B33" t="n">
+        <v>4042</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>0.1082879436617858</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 0.1036</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4072~4085</t>
-        </is>
+      <c r="B34" t="n">
+        <v>4072</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>0.08918101883531193</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 0.1109</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4088~4101</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4088</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>0.1034892584293772</v>

--- a/workspaces/btc_daily_14days/ma/ma_ratio_7.xlsx
+++ b/workspaces/btc_daily_14days/ma/ma_ratio_7.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that MA Ratio-7 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that MA Ratio-7 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -568,833 +568,833 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.09812</t>
+          <t>X ≈ -0.09806</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>21</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-4.859772930135072</v>
+        <v>-4.847294764629552</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-11.21508793219144</v>
+        <v>-11.2022248852123</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-6.862993243182579</v>
+        <v>-6.85002615644423</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-1.98434004484082</v>
+        <v>-1.971394359155596</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-7.273207523815358</v>
+        <v>-7.260130097664266</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-11.73033454525561</v>
+        <v>-11.7173234986883</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-2.310402034379898</v>
+        <v>-2.297359698850265</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1.977331289834439</v>
+        <v>1.990493217627666</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-7.59508761280577</v>
+        <v>-7.581907750296608</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-3.689129135341432</v>
+        <v>-3.675738326576131</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-8.652978156377294</v>
+        <v>-8.639532562513025</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-13.38031293627258</v>
+        <v>-13.36686901200417</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-4.282280474702247</v>
+        <v>-4.268728086069821</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.7283047254303696</v>
+        <v>0.7178750897343846</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.09077</t>
+          <t>X ≈ -0.09074</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>26</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>12.84899529283389</v>
+        <v>12.86148695419278</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>7.411299806509028</v>
+        <v>7.424175861161679</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3.183127789785381</v>
+        <v>3.196101108189119</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-8.196024200580801</v>
+        <v>-8.183082709010243</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-12.57257653985441</v>
+        <v>-12.55950245980338</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-4.601321753149655</v>
+        <v>-4.588307657838008</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-12.36619665146949</v>
+        <v>-12.35315890710817</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-8.995422477986828</v>
+        <v>-8.98226478784715</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-5.216968523947685</v>
+        <v>-5.203788180569184</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-13.75238656071738</v>
+        <v>-13.73899839051456</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-10.11701856795491</v>
+        <v>-10.10357339706923</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-13.92941538324592</v>
+        <v>-13.91597164226661</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-14.35303629707123</v>
+        <v>-14.33948457036647</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-6.414552417424602</v>
+        <v>-6.424982053120999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.08343</t>
+          <t>X ≈ -0.08341</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-4.332384176024462</v>
+        <v>-6.033928965638651</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1.445935038821951</v>
+        <v>3.041375574067587</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-13.72223434798149</v>
+        <v>-11.59864563328792</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-6.206418004204458</v>
+        <v>-4.346222273728451</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-3.049402604082786</v>
+        <v>-1.320592319920543</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-6.44936780652025</v>
+        <v>-8.152508167352941</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-6.535625481275005</v>
+        <v>-8.239165961329974</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-10.7020980830337</v>
+        <v>-12.27386988926405</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-7.066430057763426</v>
+        <v>-8.770685740876075</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-4.217549421407909</v>
+        <v>-6.054166397779781</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-4.423168838492913</v>
+        <v>-2.691429459164453</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>3.01380076474512</v>
+        <v>4.481547952025146</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>2.594355393157819</v>
+        <v>0.4920329521522433</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-4.562700565574431</v>
+        <v>-6.424982053122754</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.0761</t>
+          <t>X ≈ -0.07608</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-2.486339342106781</v>
+        <v>-1.413463869772634</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-12.40114363817775</v>
+        <v>-13.6257097834909</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-4.487889329487722</v>
+        <v>-5.535841989220451</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-6.437033183768314</v>
+        <v>-7.529490149276249</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.7397006857090105</v>
+        <v>-1.699616481889656</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-2.521857424870831</v>
+        <v>-1.402890113856046</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-8.846143487851073</v>
+        <v>-7.859621645953418</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.9942602340128417</v>
+        <v>0.1696621712351103</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-1.055320673980063</v>
+        <v>0.1089091895162468</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-3.986220924445014</v>
+        <v>-2.865777048410202</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-6.273557053160332</v>
+        <v>-7.323145677284828</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-8.323102000855798</v>
+        <v>-9.417260953205307</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-10.82819804292811</v>
+        <v>-9.839711143142715</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-12.66455241742365</v>
+        <v>-11.74413098929297</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.06876</t>
+          <t>X ≈ -0.06874</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>47</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4.936020005836113</v>
+        <v>4.948503355971148</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>5.452890427849809</v>
+        <v>5.46576291925696</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2.938365563048599</v>
+        <v>2.951336614305362</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>13.68045940356172</v>
+        <v>13.69341269841103</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>8.901319994962485</v>
+        <v>8.91440435663138</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2.830822417848204</v>
+        <v>2.843838602696309</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>4.870874887555921</v>
+        <v>4.883918597498138</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>6.529720236357086</v>
+        <v>6.542882515510698</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>6.470575756599573</v>
+        <v>6.483758772714019</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>5.622864969607853</v>
+        <v>5.636257102061734</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>7.545768920396107</v>
+        <v>7.559216764714712</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>5.455430369961206</v>
+        <v>5.468876088533193</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.909497777906878</v>
+        <v>2.923050348348717</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>1.032256093213704</v>
+        <v>1.021826457515552</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.06143</t>
+          <t>X ≈ -0.06141</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>58</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>6.105491696508281</v>
+        <v>6.117975129432097</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2.782822142096315</v>
+        <v>2.79569159620619</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>10.98563887493374</v>
+        <v>10.99861492777581</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>9.398594155441153</v>
+        <v>9.411544131158379</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>8.864167529559296</v>
+        <v>8.877251295050336</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>5.722703219968629</v>
+        <v>5.735720266205497</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>10.80266939527981</v>
+        <v>10.81571533102174</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>8.61718332151186</v>
+        <v>8.63034600036633</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>3.392905014952021</v>
+        <v>3.406086629940539</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-4.344950756731635</v>
+        <v>-4.331561608885025</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.617763748143723</v>
+        <v>0.6312099824948021</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.6522696418838407</v>
+        <v>0.6657145568685934</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-6.66251009758043</v>
+        <v>-6.648958258479979</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-9.86282827949357</v>
+        <v>-9.873257915191722</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.0541</t>
+          <t>X ≈ -0.05407</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.665954122481203</v>
+        <v>2.304137583362319</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-5.476758962116214</v>
+        <v>-4.762158248776316</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-7.2575062378571</v>
+        <v>-6.523649193307598</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-5.744286496745332</v>
+        <v>-5.029239701358421</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-3.511368094733001</v>
+        <v>-2.833963105159299</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>3.71505270383399</v>
+        <v>4.297639496959356</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-3.300288370500937</v>
+        <v>-2.622570531401642</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-7.927957778599122</v>
+        <v>-7.192959061766111</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-9.377745226057776</v>
+        <v>-8.623534064774219</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-8.84196256368439</v>
+        <v>-8.106351947718828</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-9.04892523422545</v>
+        <v>-8.313068206838395</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-9.016965036410213</v>
+        <v>-8.280918609229516</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-6.662449602916688</v>
+        <v>-5.964146657761759</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-9.192330195202381</v>
+        <v>-8.479776573670705</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.04676</t>
+          <t>X ≈ -0.04674</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>6.518107291571617</v>
+        <v>6.032730837450764</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>7.317203248660405</v>
+        <v>6.861378224981223</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>3.321040869638772</v>
+        <v>2.821242267447595</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>3.451709042243287</v>
+        <v>2.951751438320663</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>5.319586830020384</v>
+        <v>4.848945483686187</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>3.213805742865617</v>
+        <v>2.71364906243241</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.7251638688439712</v>
+        <v>0.1955674510728187</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.2587687389775581</v>
+        <v>-0.2708522044545205</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1.401405138319745</v>
+        <v>0.8863362305420139</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-4.261503869693492</v>
+        <v>-4.83521171877225</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-3.263479144443643</v>
+        <v>-3.822604391124912</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-2.02589054093081</v>
+        <v>-2.570482632514967</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.446643402180463</v>
+        <v>-2.991274987165383</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.9928656704366503</v>
+        <v>-1.546933272634945</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.03943</t>
+          <t>X ≈ -0.0394</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-2.898513459151374</v>
+        <v>-3.2910219641929</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.208820015536809</v>
+        <v>-1.628057861827564</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>7.459895214273644</v>
+        <v>6.966350620244306</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3.471001199319787</v>
+        <v>3.01106844176978</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>6.232597260950477</v>
+        <v>6.563259011141533</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>5.707101750731205</v>
+        <v>5.226700072729471</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.1494279037820263</v>
+        <v>0.2354617768581733</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.034109032571443</v>
+        <v>1.405695273171496</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>4.274933891802888</v>
+        <v>4.619582872927168</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>3.427100557435338</v>
+        <v>3.772052123027656</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.571829644688044</v>
+        <v>1.111480163373756</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.697414952406255</v>
+        <v>-2.13081577741535</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.4656729259727399</v>
+        <v>-0.9126349081648328</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1.436687251996879</v>
+        <v>1.771739258352653</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.03209</t>
+          <t>X ≈ -0.03207</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.820515622986036</v>
+        <v>-2.473689793736042</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.9250080356351091</v>
+        <v>1.308473468576722</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-4.152690856753892</v>
+        <v>-3.800666911738205</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.6606638659758204</v>
+        <v>1.044413554815307</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.5455443134675377</v>
+        <v>-0.8400629005477356</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.2482062973108015</v>
+        <v>0.1312972479319257</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>5.695929638211616</v>
+        <v>5.441936993191469</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.211156987864747</v>
+        <v>0.9300459146953486</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1.150740946135187</v>
+        <v>0.8695700118888254</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.3021792997723907</v>
+        <v>0.02113683818074463</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>3.450414204662643</v>
+        <v>3.867111832774846</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.209506110555708</v>
+        <v>-0.8244219951628153</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.630104157958044</v>
+        <v>-1.244808089685812</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.30356838794453</v>
+        <v>1.007450379309681</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.02475</t>
+          <t>X ≈ -0.02474</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.8983847249216197</v>
+        <v>-0.6293041375633024</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.6838135730501165</v>
+        <v>0.9364124192835988</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.355068424677789</v>
+        <v>1.602176139692645</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.4199910523778669</v>
+        <v>0.6728126886403558</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-2.253476881367519</v>
+        <v>-1.989079507538101</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.534718511457001</v>
+        <v>1.492602726328919</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.9173334263898028</v>
+        <v>1.165948633359562</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.08230255086295557</v>
+        <v>0.1693435665381102</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.210931130380608</v>
+        <v>-0.9535089741977529</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.4577518784480219</v>
+        <v>-0.2085666304451266</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.4058917231571755</v>
+        <v>0.6495229640350644</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.5093727306365</v>
+        <v>1.747389334669371</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>2.158765389188069</v>
+        <v>2.39127270137935</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2.943736352628875</v>
+        <v>3.149486031983628</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.01742</t>
+          <t>X ≈ -0.01741</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2.129569782056713</v>
+        <v>1.780841972165085</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.5105543624217006</v>
+        <v>0.3547733386375853</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>4.021755005860435</v>
+        <v>3.681025203153482</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.816978419373747</v>
+        <v>0.6632380536555047</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.1091448416735616</v>
+        <v>-0.2478500237757046</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.4059291493809241</v>
+        <v>0.251747668512877</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.161509977801046</v>
+        <v>-1.321499778216058</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-2.369805515337085</v>
+        <v>-2.532497691915843</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.9466863934027714</v>
+        <v>-1.103869330573197</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.424446050920771</v>
+        <v>-1.580084345523133</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.743861142061824</v>
+        <v>-2.903650988206742</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-3.081800032239649</v>
+        <v>-3.243028653099131</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.759842779636621</v>
+        <v>-2.918242176633768</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.6524706330379857</v>
+        <v>-0.8279671277495311</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.01008</t>
+          <t>X ≈ -0.01007</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.5642944193313042</v>
+        <v>-0.5635194834860116</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.480363654860746</v>
+        <v>-2.174566689403861</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2.484495802643444</v>
+        <v>2.151224623261257</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3.369837590796308</v>
+        <v>2.871592373399366</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>4.617473731822827</v>
+        <v>4.264190576317851</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2.830969249247595</v>
+        <v>2.495322039019577</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.747188282532413</v>
+        <v>2.706660599484479</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.98235628090967</v>
+        <v>1.947108977124778</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.921881065806076</v>
+        <v>1.887040151591243</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.1757624477472177</v>
+        <v>0.1532822503537474</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.22257994270894</v>
+        <v>-1.233462574243752</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.487969614094787</v>
+        <v>-1.495133270033932</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.910334622792618</v>
+        <v>-1.915977258183631</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-2.981716596529083</v>
+        <v>-2.874686195134657</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.002748</t>
+          <t>X ≈ -0.002735</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.1005236913592356</v>
+        <v>-0.07702433681787824</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.2328062723476378</v>
+        <v>-0.08769089316277956</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.216381084127569</v>
+        <v>-1.963636216123405</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.0322288104804187</v>
+        <v>0.2299317408974488</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.3421629228678853</v>
+        <v>-0.07882797927261009</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.8681141136679642</v>
+        <v>1.135578550117188</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.4508459538186216</v>
+        <v>0.363239514520842</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.8992730732530845</v>
+        <v>0.9397593256832479</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.981065736567047</v>
+        <v>2.026382632859367</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.133775613323373</v>
+        <v>1.179961848508505</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.158211904861957</v>
+        <v>1.205566089177239</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.336633848919554</v>
+        <v>2.388907595310819</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.230463092404321</v>
+        <v>1.280236367209497</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.022518520790506</v>
+        <v>1.046282314693336</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.004587</t>
+          <t>X ≈ 0.004598</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-3.091181042625522</v>
+        <v>-2.956826900754187</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.074767644823559</v>
+        <v>-0.9487718014060533</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.472043926856259</v>
+        <v>-1.345952099139105</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-2.791240106364114</v>
+        <v>-2.661676970606521</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.879309168532387</v>
+        <v>-1.753113166279654</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.099971405651289</v>
+        <v>-0.9750104404687505</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.9891678983198133</v>
+        <v>1.108903108726359</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.2837783141501617</v>
+        <v>0.4038037512992076</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.192964092311435</v>
+        <v>-2.065705951369125</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.6239679274276568</v>
+        <v>-0.5026656362099686</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.103335551274867</v>
+        <v>0.01612750223797121</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.489162683826429</v>
+        <v>-2.362326046776062</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.9742011104756472</v>
+        <v>-0.8525458790447686</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.93513353122605</v>
+        <v>-1.835610072446372</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.01192</t>
+          <t>X ≈ 0.01193</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.079611722804167</v>
+        <v>-1.219375022717237</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.682418276532417</v>
+        <v>-2.82178918595659</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-3.705304676479358</v>
+        <v>-3.84654385014867</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-3.888161204984421</v>
+        <v>-4.030410661168659</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.819875054847287</v>
+        <v>1.697394388473718</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.491322466728484</v>
+        <v>1.366809430169624</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2.968540312768212</v>
+        <v>2.848960103504332</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>2.507740291088091</v>
+        <v>2.386164963991156</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>3.700545931624809</v>
+        <v>3.582338788907123</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>3.481736291453508</v>
+        <v>3.366259285018693</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>2.027017007182749</v>
+        <v>1.908624415709077</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>2.689378935734261</v>
+        <v>2.57302263370233</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>3.523814024593783</v>
+        <v>3.410888084442021</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>4.400494604518968</v>
+        <v>4.266841846248248</v>
       </c>
     </row>
     <row r="22">
@@ -1407,98 +1407,98 @@
         <v>286</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-2.686595543580594</v>
+        <v>-2.674073253904972</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.528917408601515</v>
+        <v>-1.516007599025464</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.567506350018284</v>
+        <v>-1.554499218600682</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.435644216612879</v>
+        <v>-1.422665074214414</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-3.7125575696396</v>
+        <v>-3.699446765264661</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-3.063662869137829</v>
+        <v>-3.050619972843464</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-4.891715726758513</v>
+        <v>-4.878649472458036</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.088119854194879</v>
+        <v>-3.263281885894493</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.454306336330383</v>
+        <v>-2.43958360671003</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.268341052201002</v>
+        <v>-2.25279381184879</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-3.676003212481533</v>
+        <v>-3.860389395317753</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.9973291074848376</v>
+        <v>-1.184825111472755</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.41951850494565</v>
+        <v>-1.403857131002539</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-3.267699270571491</v>
+        <v>-3.278128906269643</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.02659</t>
+          <t>X ≈ 0.0266</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-2.711216683975707</v>
+        <v>-2.908270864054394</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.3229242234940699</v>
+        <v>0.106673878659862</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-5.143366566618887</v>
+        <v>-5.338123957143317</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-3.744049152040787</v>
+        <v>-3.523137496743985</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-4.704417340132984</v>
+        <v>-4.902654635495203</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-5.674428002932586</v>
+        <v>-5.86738807805483</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-7.874089781105177</v>
+        <v>-8.058094432286588</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-5.383704702967137</v>
+        <v>-5.159010962797574</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-4.180544770258187</v>
+        <v>-3.957176063894842</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.923967035225772</v>
+        <v>-3.130741159513775</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-3.13298966748853</v>
+        <v>-2.921833692886381</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-3.94784301557231</v>
+        <v>-3.733108769566051</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.00325680054835</v>
+        <v>-2.044617805026071</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-3.4484507225093</v>
+        <v>-3.260425091097389</v>
       </c>
     </row>
     <row r="24">
@@ -1508,101 +1508,101 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>4.518514806206738</v>
+        <v>4.818407574781112</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.393665955171691</v>
+        <v>1.686281311853335</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-4.520369504585929</v>
+        <v>-4.255528086490074</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-7.398884059789864</v>
+        <v>-7.653252596505816</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-5.426519627157518</v>
+        <v>-5.164078533132674</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-11.15009230625973</v>
+        <v>-10.91812496591278</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-10.23460953741326</v>
+        <v>-9.997577198047644</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-7.191177384726331</v>
+        <v>-7.440299354718839</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-10.27732683340279</v>
+        <v>-10.52718656303382</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-5.822392690376809</v>
+        <v>-5.845835610854863</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-6.529658577508457</v>
+        <v>-6.769995507441706</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-6.495275420163026</v>
+        <v>-6.735617355086383</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-8.423067719550104</v>
+        <v>-8.670919723551279</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-5.660783573203496</v>
+        <v>-5.919931548072249</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.04126</t>
+          <t>X ≈ 0.04127</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>139</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-2.51437395265642</v>
+        <v>-2.501851662980798</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.989561436428758</v>
+        <v>-1.976651626852707</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-3.111467560710217</v>
+        <v>-3.098460429292615</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-6.578336730261036</v>
+        <v>-6.565357587862572</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-7.827617828854919</v>
+        <v>-7.81450702447998</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-2.502769245027658</v>
+        <v>-2.489726348733292</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.155315379033119</v>
+        <v>-1.142249124732643</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-2.34097161858967</v>
+        <v>-2.327790609294432</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.8915841269131448</v>
+        <v>0.484166977626117</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.836238899841391</v>
+        <v>-2.822833772188559</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-2.321567763727323</v>
+        <v>-2.308110470017105</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.567760145950231</v>
+        <v>-1.554307857230121</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.268590296463522</v>
+        <v>-1.255034250111919</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.738293424618846</v>
+        <v>-1.748723060316998</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>123</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-3.712950515331876</v>
+        <v>-3.700428225656253</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.259483477889681</v>
+        <v>-1.24657366831363</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.8413440544050133</v>
+        <v>-0.8283369229874111</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.914925338365137</v>
+        <v>0.9279044807636012</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-2.062520266950898</v>
+        <v>-2.049409462575959</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-2.57808645931653</v>
+        <v>-2.565043563022165</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1.40222047381765</v>
+        <v>1.415286728118126</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>2.561053335198707</v>
+        <v>2.574234344493945</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.687045318935141</v>
+        <v>1.700244057889904</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.649928263988521</v>
+        <v>1.663333391641352</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>3.884199329914892</v>
+        <v>3.89765662362511</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>8.796631267748126</v>
+        <v>8.810083556468236</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>7.563368526721881</v>
+        <v>7.576924573073484</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>4.56105733867291</v>
+        <v>4.550627702974758</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>91</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.943987770759485</v>
+        <v>-1.931465481083862</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-4.654462482624751</v>
+        <v>-4.6415526730487</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.544075404185222</v>
+        <v>1.557082535602824</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2.773229635693816</v>
+        <v>2.786208778092281</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>4.43261061842378</v>
+        <v>4.445721422798719</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2.532250358337308</v>
+        <v>2.545293254631673</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.8491866556382632</v>
+        <v>-0.8361204013377872</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.316370054419664</v>
+        <v>-1.303189045124427</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.377369940602065</v>
+        <v>-1.364171201647302</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>4.365911467776598</v>
+        <v>4.37931659542943</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>4.161158143458962</v>
+        <v>4.17461543716918</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>4.195541300804393</v>
+        <v>4.208993589524503</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>4.874187788760651</v>
+        <v>4.887743835112254</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>5.123909121036938</v>
+        <v>5.113479485338786</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>74</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-3.844789671561323</v>
+        <v>-3.8322673818857</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-2.753660581822921</v>
+        <v>-2.740750772246869</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.445826585716766</v>
+        <v>-0.4328194542991639</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-5.72097885851467</v>
+        <v>-5.707999716116205</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-8.962102776289541</v>
+        <v>-8.948991971914602</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-4.610606784519831</v>
+        <v>-4.597563888225466</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-8.749394555846159</v>
+        <v>-8.736328301545683</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-7.865226603276355</v>
+        <v>-7.852045593981117</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-5.223523786755912</v>
+        <v>-5.210325047801149</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-4.722297620432492</v>
+        <v>-4.708892492779661</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-4.927050944750071</v>
+        <v>-4.913593651039854</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-6.244019138755988</v>
+        <v>-6.230566850035878</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-5.312922398349542</v>
+        <v>-5.299366351997939</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.00914701201912</v>
+        <v>-1.019576647717273</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>62</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.7323681314028789</v>
+        <v>0.7448904210785017</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>10.41111709908383</v>
+        <v>10.42402690865988</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.564635489261441</v>
+        <v>3.577642620679043</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>5.307791847675389</v>
+        <v>5.320770990073854</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>4.76937063260322</v>
+        <v>4.782481436978159</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.2281028928995212</v>
+        <v>0.2411457891938866</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>6.5949820788531</v>
+        <v>6.608048333153576</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>1.289089002652247</v>
+        <v>1.302270011947485</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-3.610620560949464</v>
+        <v>-3.597421821994701</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-6.07364897178384</v>
+        <v>-6.060243844131008</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>8.237726736156645</v>
+        <v>8.251184029866863</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>8.272109893502076</v>
+        <v>8.285562182222186</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>3.013145605137822</v>
+        <v>3.026701651489425</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.03706048580121291</v>
+        <v>0.02663085010306077</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>65</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>16.73733091055932</v>
+        <v>16.74985320023494</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>8.971911143748841</v>
+        <v>8.984820953324892</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>5.500119360229178</v>
+        <v>5.51312649164678</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>7.168834031298175</v>
+        <v>7.181813173696639</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>3.553489739302975</v>
+        <v>3.566600543677914</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>3.850931677018636</v>
+        <v>3.863974573313001</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5.30465949820789</v>
+        <v>5.317725752508366</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>4.837476099426389</v>
+        <v>4.850657108721627</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>3.238014674782555</v>
+        <v>3.251213413737318</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>7.003274105139283</v>
+        <v>7.016679232792114</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>3.721597703898532</v>
+        <v>3.735054997608749</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>3.755980861244012</v>
+        <v>3.769433149964122</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.2588031733760303</v>
+        <v>0.2723592197276332</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>2.046986044113865</v>
+        <v>2.036556408415713</v>
       </c>
     </row>
     <row r="31">
@@ -1875,150 +1875,150 @@
         <v>37</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>20.47953465276296</v>
+        <v>20.49205694243859</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>18.86796103979874</v>
+        <v>18.88087084937479</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>18.47309233320215</v>
+        <v>18.48609946461975</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>24.00875087121513</v>
+        <v>24.0217300136136</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>15.36222154803478</v>
+        <v>15.37533235240972</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>18.36236618845311</v>
+        <v>18.37540908474747</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>23.68303787658616</v>
+        <v>23.69610413088664</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>23.21585447780466</v>
+        <v>23.2290354870999</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>20.45215188891977</v>
+        <v>20.46535062787453</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>22.30472940659446</v>
+        <v>22.31813453424729</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>16.69457067687168</v>
+        <v>16.7080279705819</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>19.43165653691973</v>
+        <v>19.44510882563984</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>19.01140192597479</v>
+        <v>19.02495797232639</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>19.26112325825108</v>
+        <v>19.25069362255292</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.09261</t>
+          <t>X ≈ 0.0926</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>34</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>6.330091091554735</v>
+        <v>6.342613381230358</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>7.65969394917871</v>
+        <v>7.672603758754761</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>4.323648771993888</v>
+        <v>4.33665590341149</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>19.15978425754256</v>
+        <v>19.17276339994103</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>15.68018657188216</v>
+        <v>15.6932973762571</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>15.97762850959785</v>
+        <v>15.99067140589221</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>10.01054185114911</v>
+        <v>10.02360810544958</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>12.48453492295584</v>
+        <v>12.49771593225108</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>24.18824091912644</v>
+        <v>24.2014396580812</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>23.33811573409851</v>
+        <v>23.35152086175134</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>20.19218593919265</v>
+        <v>20.20564323290287</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>17.28539262594985</v>
+        <v>17.29884491466996</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>22.74749095618146</v>
+        <v>22.76104700253306</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>20.05603581786951</v>
+        <v>20.04560618217136</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.09994</t>
+          <t>X ≈ 0.09993</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>30</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.480916030534353</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.7716785998408753</v>
+        <v>-0.7587687902648241</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>5.500119360229178</v>
+        <v>5.51312649164678</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>8.963705826170028</v>
+        <v>8.976684968568492</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>8.425284611097837</v>
+        <v>8.438395415472776</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>12.05605988214683</v>
+        <v>12.06910277844119</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>8.637992831541219</v>
+        <v>8.651059085841695</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>8.170809432759718</v>
+        <v>8.183990442054956</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>11.44314287991075</v>
+        <v>11.45634161886551</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>10.59301769488282</v>
+        <v>10.60642282253565</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>17.05493103723191</v>
+        <v>17.06838833094213</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>13.75598086124401</v>
+        <v>13.76943314996412</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>16.66905958363244</v>
+        <v>16.68261562998404</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>23.5854475825754</v>
+        <v>23.57501794687725</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>16</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>3.756561679790025</v>
+        <v>3.769083969465647</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>8.394988066825725</v>
+        <v>8.407897876401776</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1.750119360229178</v>
+        <v>1.76312649164678</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-4.369627507163365</v>
+        <v>-4.356648364764901</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1.341951277764508</v>
+        <v>1.355062082139447</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.639393215480169</v>
+        <v>1.652436111774534</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>7.804659498207847</v>
+        <v>7.817725752508323</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>13.58747609942639</v>
+        <v>13.60065710872163</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>13.52647621324409</v>
+        <v>13.53967495219885</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>12.67635102821616</v>
+        <v>12.68975615586899</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>12.47159770389858</v>
+        <v>12.4850549976088</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>18.75598086124405</v>
+        <v>18.76943314996416</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>18.33572625029911</v>
+        <v>18.34928229665071</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>18.58544758257544</v>
+        <v>18.57501794687729</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that MA Ratio-7 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that MA Ratio-7 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2210,989 +2210,989 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.1018</t>
+          <t>X &gt; -0.1017</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4088</v>
+        <v>4089</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.286659485779353</v>
+        <v>-0.2868643484280611</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.1050119331742323</v>
+        <v>-0.1052696437152321</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.267140947162865</v>
+        <v>-0.2673613132312624</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.2212624510383847</v>
+        <v>-0.2214934489317315</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1362644898703422</v>
+        <v>-0.1365191770113583</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.02806509048016892</v>
+        <v>0.02777172319752452</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.005514199062595537</v>
+        <v>0.005225752508366099</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.05749214678758108</v>
+        <v>-0.05776779970327794</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.04156294669143534</v>
+        <v>0.0412626415002677</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.06191876650525074</v>
+        <v>-0.06219840069099547</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.008541626338526953</v>
+        <v>-0.008835520475258818</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.03375019010072577</v>
+        <v>-0.03403788401290342</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.04896438310758811</v>
+        <v>-0.04925071068424813</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.0300123000077761</v>
+        <v>-0.02977540112959787</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.09444</t>
+          <t>X &gt; -0.09441</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4067</v>
+        <v>4068</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.2630461633472265</v>
+        <v>-0.2633223035066621</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.0476449314581302</v>
+        <v>-0.04798447653936222</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.2330831900405599</v>
+        <v>-0.2333800050435855</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.2121587801581697</v>
+        <v>-0.212460037153285</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.09941280466924951</v>
+        <v>-0.09974537432363206</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.08877971854764866</v>
+        <v>0.08840274572938966</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.01747245844353529</v>
+        <v>0.01711225557584584</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.06799898036737773</v>
+        <v>-0.06834141852431941</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.08099487729123922</v>
+        <v>0.08061529101544807</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.04318962518595981</v>
+        <v>-0.04354443352197279</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.03609401839489124</v>
+        <v>0.03571822531697677</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.03516493595524395</v>
+        <v>0.03478941532038959</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.02710560810796636</v>
+        <v>-0.02746874783196063</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.03392787845238843</v>
+        <v>-0.03363495381104542</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.0871</t>
+          <t>X &gt; -0.08708</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4041</v>
+        <v>4042</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.347409706495128</v>
+        <v>-0.3477471032840427</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.0956361621404227</v>
+        <v>-0.09604884288776816</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.2550632656345897</v>
+        <v>-0.255440002308319</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.160790183045826</v>
+        <v>-0.16118933218835</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.01915983334660609</v>
+        <v>-0.01959849549570691</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.1189560705061083</v>
+        <v>0.1184854944905851</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.09714961678496792</v>
+        <v>0.09668351985833112</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.01055948248613703</v>
+        <v>-0.01100297032975561</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.1150822438916421</v>
+        <v>0.114607000629789</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.0450160467575742</v>
+        <v>0.04455101498911063</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.1014196623555605</v>
+        <v>0.1009388047781457</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.1250137576081016</v>
+        <v>0.1245271163340504</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.0650681602446852</v>
+        <v>0.06459270971031827</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.007125385099527648</v>
+        <v>0.007477125501686999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.07977</t>
+          <t>X &gt; -0.07974</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>4014</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.320604945489336</v>
+        <v>-0.3080826558137133</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.1060054751513846</v>
+        <v>-0.1179342150040412</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.1644769130627495</v>
+        <v>-0.1763145021420414</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.1201245250559637</v>
+        <v>-0.1319962772897156</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.001222965559691147</v>
+        <v>-0.01052330190231032</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.1631376212484454</v>
+        <v>0.1761805175428108</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.1417646959199033</v>
+        <v>0.1548309502203793</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.06135669644131525</v>
+        <v>0.07453770573655305</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.1633883804498595</v>
+        <v>0.1765871194046227</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.07368801179007534</v>
+        <v>0.08709313944290642</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.13185411415499</v>
+        <v>0.1204172082137234</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.1055824548695128</v>
+        <v>0.09413434518324948</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.04805501742239926</v>
+        <v>0.06161106377400216</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.03786412467804467</v>
+        <v>0.05234729416174844</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.07243</t>
+          <t>X &gt; -0.07241</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3966</v>
+        <v>3967</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.2943933340325415</v>
+        <v>-0.2949863822931533</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.04280103816815028</v>
+        <v>0.04210245041538485</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.112151195466069</v>
+        <v>-0.1128161931194356</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.0436717727568805</v>
+        <v>-0.04435266448826525</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.0101902714751958</v>
+        <v>0.009488641495579486</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.1956337791439822</v>
+        <v>0.1948889419632138</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.2505442200805277</v>
+        <v>0.2497841319748986</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.07413269559960867</v>
+        <v>0.07341069543192447</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.1781382631055877</v>
+        <v>0.1773889501847492</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.1228245798534431</v>
+        <v>0.1220779891603527</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.2093780012026798</v>
+        <v>0.2086066348883975</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.2075937644698271</v>
+        <v>0.2068229206872232</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.1796889425098485</v>
+        <v>0.1789193934248985</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.1915998770786729</v>
+        <v>0.1921089476334856</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.0651</t>
+          <t>X &gt; -0.06507</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3919</v>
+        <v>3920</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.357120924482615</v>
+        <v>-0.3578547541549923</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.02208138115184255</v>
+        <v>-0.0229261317365328</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.1487356016028869</v>
+        <v>-0.1495547599431504</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.208263292350388</v>
+        <v>-0.2090656675638414</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.09643976093202866</v>
+        <v>-0.09727948059916258</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.164030343058478</v>
+        <v>0.1631285761329835</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.1951332628538438</v>
+        <v>0.1942218054750029</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.003288231783805884</v>
+        <v>-0.004156951390442032</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.1026739706345055</v>
+        <v>0.1017768630268776</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.05686339120366313</v>
+        <v>0.05596410693933507</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.121393726336116</v>
+        <v>0.1204743195562941</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.1446572193159312</v>
+        <v>0.1437319770931467</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.1469507400950292</v>
+        <v>0.1460178233020812</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.181518008704515</v>
+        <v>0.1821608040200999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.05776</t>
+          <t>X &gt; -0.05774</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3861</v>
+        <v>3862</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.4542023883565989</v>
+        <v>-0.4551095789214514</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.06421668401337399</v>
+        <v>-0.06525648601428458</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.3159963422501662</v>
+        <v>-0.3169793694428193</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.3525776492454682</v>
+        <v>-0.3535491912111439</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.2310461382561613</v>
+        <v>-0.2320601085089677</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.08052787559905994</v>
+        <v>0.07943869575386486</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.03578669572598159</v>
+        <v>0.03470688458383364</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.1327850849542642</v>
+        <v>-0.1338309988274986</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.05324807046085311</v>
+        <v>0.05215232483914889</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.1229875094580706</v>
+        <v>0.1218565180003992</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.1139372484120429</v>
+        <v>0.112804027363012</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.1370318578787533</v>
+        <v>0.1358927772933143</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.2492425630904123</v>
+        <v>0.2480656256696108</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.3324043295321459</v>
+        <v>0.3331743425271654</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.05043</t>
+          <t>X &gt; -0.05041</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>3789</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.4944903980637321</v>
+        <v>-0.5082700547321437</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.03863447566553901</v>
+        <v>0.02523541915373073</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.1840911660866169</v>
+        <v>-0.1973998241426997</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.2501223742335981</v>
+        <v>-0.2634659483394799</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.1687122293444929</v>
+        <v>-0.1819310721522882</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.01146327078699727</v>
+        <v>-0.001830414430358474</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.09918004615309428</v>
+        <v>0.08590278095937265</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.01534171207461554</v>
+        <v>0.002172260236775969</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.2324593445039795</v>
+        <v>0.2193006770275332</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.2933428552659905</v>
+        <v>0.2803836275273142</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.2880534001011128</v>
+        <v>0.2751393857944535</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.3109795423307986</v>
+        <v>0.2980535667406983</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.3805811315656058</v>
+        <v>0.3677519536428022</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.5133969095746025</v>
+        <v>0.5029672738764503</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.04309</t>
+          <t>X &gt; -0.04307</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3706</v>
+        <v>3707</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.6515453382255671</v>
+        <v>-0.6529590412870405</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.1243771833087166</v>
+        <v>-0.1259821988872361</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.2625925041776043</v>
+        <v>-0.2641731318066931</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.3330290141600898</v>
+        <v>-0.3345875630430442</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.2916288029891945</v>
+        <v>-0.2932156358368729</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.06025675759468641</v>
+        <v>-0.06189767019046855</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.08516044084188223</v>
+        <v>0.08347696414003281</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.009889892529834299</v>
+        <v>0.008211646830972086</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.2062795007676712</v>
+        <v>0.2045456418540255</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.3953537236339528</v>
+        <v>0.3935421973672391</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.3675939292962553</v>
+        <v>0.3657827604120314</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.3633163520746479</v>
+        <v>0.3615064850948855</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.4438999756835145</v>
+        <v>0.4420546806852315</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.5471313386466363</v>
+        <v>0.5483117154232389</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.03576</t>
+          <t>X &gt; -0.03574</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>3585</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.5757062468358711</v>
+        <v>-0.5631839571602484</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.08777534713030377</v>
+        <v>-0.07486553755425263</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.5232399278687083</v>
+        <v>-0.5102327964511062</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.4614216657168697</v>
+        <v>-0.4484425233184055</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.5118328068209124</v>
+        <v>-0.5265461538093561</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.25491516192033</v>
+        <v>-0.2418722656259646</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.0930782064484319</v>
+        <v>0.0783048170963454</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.02467928904479066</v>
+        <v>-0.03934567601799444</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.06895532187918008</v>
+        <v>0.05429890763060996</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.2930269825209848</v>
+        <v>0.2785691957129615</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.326948874467142</v>
+        <v>0.3404061681773598</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.4328696262286797</v>
+        <v>0.4463219149487898</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.4745996468412201</v>
+        <v>0.488155693192823</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.5171072757413668</v>
+        <v>0.5066776400432147</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.02842</t>
+          <t>X &gt; -0.0284</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3436</v>
+        <v>3437</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.4783614863450794</v>
+        <v>-0.4809160305343525</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.1316940677449949</v>
+        <v>-0.1344332340649856</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.3658510488221722</v>
+        <v>-0.3685440419959107</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.5100802059445186</v>
+        <v>-0.5127261135319046</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.5103709283312838</v>
+        <v>-0.5130458691083746</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.2552060876557221</v>
+        <v>-0.2579412467160296</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.1498859563375703</v>
+        <v>-0.1526575227529605</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.07827055949284301</v>
+        <v>-0.08108846200157416</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.02204436203804505</v>
+        <v>0.01919267445335748</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.2926300979836043</v>
+        <v>0.2896544412511517</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.1915017457712267</v>
+        <v>0.1885433697018186</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.5040902271544283</v>
+        <v>0.501041175552956</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.565868816490557</v>
+        <v>0.5627785153825329</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.4830028794322061</v>
+        <v>0.4851139608429165</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.02109</t>
+          <t>X &gt; -0.02107</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>3249</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.454186556947171</v>
+        <v>-0.4723297073206183</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.1786315650760741</v>
+        <v>-0.1963966021257875</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.4649005845391585</v>
+        <v>-0.482577712096699</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.5636115464512272</v>
+        <v>-0.5813260811552894</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.4100444238013452</v>
+        <v>-0.4276367204396152</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.3582272941913018</v>
+        <v>-0.3592346498962229</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.2113110177626254</v>
+        <v>-0.2289572941746769</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.07803849350755598</v>
+        <v>-0.09557945041815685</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.09300971047826323</v>
+        <v>0.07547704193456184</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.3358192114316552</v>
+        <v>0.3184834844887305</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.1791622795443359</v>
+        <v>0.1618692657514771</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.4462300153504444</v>
+        <v>0.4289225378447767</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.474187788760652</v>
+        <v>0.4569746043430172</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.3413724825446209</v>
+        <v>0.3309428468464688</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.01375</t>
+          <t>X &gt; -0.01374</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2980</v>
+        <v>2981</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.6874182533203381</v>
+        <v>-0.6748959636447154</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.2408433149072522</v>
+        <v>-0.2459482774443345</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.8699040589745621</v>
+        <v>-0.85689692755696</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.6882352715542197</v>
+        <v>-0.6932157786156381</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.4569108373626705</v>
+        <v>-0.4438000329877312</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.4272065167822205</v>
+        <v>-0.4141636204878552</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.125538024390039</v>
+        <v>-0.1307347561931067</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.1288357779260494</v>
+        <v>0.1235061211086403</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.1868614728755773</v>
+        <v>0.1815034853535735</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.4947156394762189</v>
+        <v>0.4891698912123701</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.4430190917631478</v>
+        <v>0.4374678662415121</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.764699841793977</v>
+        <v>0.7590409273694192</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.7661187360421522</v>
+        <v>0.7604157641222145</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.4310851664680158</v>
+        <v>0.4351320025632504</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.006416</t>
+          <t>X &gt; -0.006402</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2645</v>
+        <v>2643</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.7030123873038292</v>
+        <v>-0.6891393424921048</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.04280103816815028</v>
+        <v>0.0006930480351670099</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.294752434642618</v>
+        <v>-1.24159048948529</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.202206692683681</v>
+        <v>-1.149101194953538</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.099602266730216</v>
+        <v>-1.045881314086969</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.8398677196631184</v>
+        <v>-0.7862431335084779</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.4893804867034603</v>
+        <v>-0.4935950022086146</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.1059201269886998</v>
+        <v>-0.1097052921843797</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.0328858101609768</v>
+        <v>-0.03660903571655183</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.5351123575212924</v>
+        <v>0.5321248751738636</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.6539739789269134</v>
+        <v>0.6511547708514343</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.050009583844165</v>
+        <v>1.047315947695694</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.105102431773595</v>
+        <v>1.102686230084899</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.8633303803069694</v>
+        <v>0.8584080338995719</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 0.0009193</t>
+          <t>X &gt; 0.0009315</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>2208</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.8222549417095237</v>
+        <v>-0.809732652033901</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.005195835570127372</v>
+        <v>0.01810564514617852</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.112346764432068</v>
+        <v>-1.099339633014466</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.43376481520307</v>
+        <v>-1.420785672804605</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.249512136869633</v>
+        <v>-1.236401332494694</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.177905790843226</v>
+        <v>-1.164862894548861</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.675466969723459</v>
+        <v>-0.662400715422983</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.3048646145365552</v>
+        <v>-0.3164612291284143</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.4314803871175741</v>
+        <v>-0.4430408182484982</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.4166269214771248</v>
+        <v>0.4044939497207096</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.5541768894189403</v>
+        <v>0.5419297149312712</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.7953651980480032</v>
+        <v>0.7830078105976028</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.080291467690422</v>
+        <v>1.067706923178555</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.8318243941696011</v>
+        <v>0.8213947584714489</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.008254</t>
+          <t>X &gt; 0.008265</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.3002123346464032</v>
+        <v>-0.3142493638676882</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.253677683705277</v>
+        <v>0.2412312097351546</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.029586358815799</v>
+        <v>-1.04242906390877</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.12143206018942</v>
+        <v>-1.13442614254263</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.104606190308786</v>
+        <v>-1.117160140082774</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.195837212060091</v>
+        <v>-1.20867499933658</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.058472095351249</v>
+        <v>-1.071163136380527</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.440301678351382</v>
+        <v>-0.4826762246117084</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.02619193572756018</v>
+        <v>-0.06857963368219089</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.6560506945120466</v>
+        <v>0.6138384695508634</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.7054596961078232</v>
+        <v>0.6632686870912607</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.551081083961158</v>
+        <v>1.508854085376143</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.552996445285181</v>
+        <v>1.510842185230096</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.468455939121363</v>
+        <v>1.434549719452491</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.01559</t>
+          <t>X &gt; 0.0156</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1476</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.131764905904987</v>
+        <v>-0.1192426162293643</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.8882404284991878</v>
+        <v>0.901150238075239</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.4512976438194016</v>
+        <v>-0.4382905124017995</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.5234736610094757</v>
+        <v>-0.5104945186110115</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.736658708740215</v>
+        <v>-1.723547904365276</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.776598687353832</v>
+        <v>-1.763555791059467</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.928808787891974</v>
+        <v>-1.915742533591498</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.077446250337289</v>
+        <v>-1.100759895326952</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.8316318948640173</v>
+        <v>-0.8551596190367974</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.0453503520836378</v>
+        <v>0.02083723695007933</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.4198385699337663</v>
+        <v>0.3949603390557215</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.305066846348957</v>
+        <v>1.279581999761149</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.127054163578244</v>
+        <v>1.101482702879551</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.8347700758003285</v>
+        <v>0.8243404401021763</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.02292</t>
+          <t>X &gt; 0.02293</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1190</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.4822532137380549</v>
+        <v>0.4947755034136776</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.469170799432639</v>
+        <v>1.48208060900869</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.1830323581279032</v>
+        <v>-0.1700252267103011</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.304246115713191</v>
+        <v>-0.2912669733147268</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.261778814440021</v>
+        <v>-1.248668010065082</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.467270657109943</v>
+        <v>-1.454227760815577</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.21671518745849</v>
+        <v>-1.203648933158014</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.5942087287378968</v>
+        <v>-0.581027719442659</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.4416445921250443</v>
+        <v>-0.4743652825035767</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.601414000508349</v>
+        <v>0.5672729343924843</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.404217351253742</v>
+        <v>1.417674644963959</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1.858415789875409</v>
+        <v>1.871868078595519</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.739087594836931</v>
+        <v>1.70360639404786</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1.820741700222463</v>
+        <v>1.810312064524311</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.03026</t>
+          <t>X &gt; 0.03027</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.272252056359065</v>
+        <v>1.341073498261458</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.752728652599828</v>
+        <v>1.82412824289397</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.044052414622477</v>
+        <v>1.115220732484474</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.5466904844684777</v>
+        <v>0.5124615828791192</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.4101407724446986</v>
+        <v>-0.3399640958710251</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.4265063661097912</v>
+        <v>-0.3567261918903881</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.43018251076019</v>
+        <v>0.5009718258068006</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.5906141747402032</v>
+        <v>0.5574633914441378</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.4832824959665984</v>
+        <v>0.391769193036545</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1.473520839536917</v>
+        <v>1.486925967189748</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>2.526629150439462</v>
+        <v>2.496859824471336</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3.294764928329968</v>
+        <v>3.265760537162443</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>2.664866711515046</v>
+        <v>2.635746095181666</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3.124231649661354</v>
+        <v>3.071345334075566</v>
       </c>
     </row>
     <row r="25">
@@ -3205,98 +3205,98 @@
         <v>755</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.4166145898429292</v>
+        <v>0.429136879518552</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.847369019206724</v>
+        <v>1.860278828782775</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.510701370811191</v>
+        <v>2.523708502228793</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>2.640954503418691</v>
+        <v>2.653933645817155</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.9120570978703313</v>
+        <v>0.9251679022452706</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.399975226062182</v>
+        <v>2.413018122356547</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>3.241167434715834</v>
+        <v>3.25423368901631</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.641708903659193</v>
+        <v>2.654889912954431</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.319522570859981</v>
+        <v>3.25528341780732</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3.39654970371285</v>
+        <v>3.409954831365681</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>4.913650684031033</v>
+        <v>4.927107977741251</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>5.875186159257261</v>
+        <v>5.888638447977371</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>5.587381879438176</v>
+        <v>5.600937925789779</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>5.439752218336992</v>
+        <v>5.429322582638839</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.04493</t>
+          <t>X &gt; 0.04494</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>616</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.077990251218594</v>
+        <v>1.090512540894217</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>2.713169885007588</v>
+        <v>2.726079694583639</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3.77934013944995</v>
+        <v>3.792347270867552</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>4.721281583745771</v>
+        <v>4.734260726144235</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>2.884159069972306</v>
+        <v>2.897269874347245</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>3.506276332363292</v>
+        <v>3.519319228657658</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>4.233230926779321</v>
+        <v>4.246297181079797</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>3.76604752799782</v>
+        <v>3.779228537293058</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>3.867385304153181</v>
+        <v>3.880584043107945</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>4.802974404839532</v>
+        <v>4.816379532492363</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>6.546273028573907</v>
+        <v>6.559730322284125</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>7.554682159945308</v>
+        <v>7.568134448665418</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>7.134427549000407</v>
+        <v>7.147983595352009</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>7.059473556601368</v>
+        <v>7.049043920903216</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>493</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2.273295959708882</v>
+        <v>2.285818249384505</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>3.704318695629013</v>
+        <v>3.717228505205064</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>4.932168041770758</v>
+        <v>4.94517517318836</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5.670940444155136</v>
+        <v>5.6839195865536</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>4.118320446121501</v>
+        <v>4.131431250496441</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>5.02428165361404</v>
+        <v>5.037324549908405</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>4.939547936341761</v>
+        <v>4.952614190642237</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>4.066685024375687</v>
+        <v>4.079866033670925</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>4.411364651377959</v>
+        <v>4.424563390332722</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>5.589637032272954</v>
+        <v>5.603042159925785</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>7.210441517286</v>
+        <v>7.223898810996218</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>7.244824674631431</v>
+        <v>7.258276963351541</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>7.027409820278827</v>
+        <v>7.04096586663043</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>7.682810665739709</v>
+        <v>7.672381030041556</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>402</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3.227954714615898</v>
+        <v>3.24047700429152</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>5.596480604139195</v>
+        <v>5.609390413715246</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>5.699124335353559</v>
+        <v>5.712131466771162</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>6.326889905771999</v>
+        <v>6.339869048170463</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>4.047175158361526</v>
+        <v>4.060285962736465</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>5.588398190604551</v>
+        <v>5.601441086898916</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>6.249933130048682</v>
+        <v>6.262999384349158</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>5.285237293456234</v>
+        <v>5.298418302751472</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>5.721749845084879</v>
+        <v>5.734948584039643</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>5.866649535678846</v>
+        <v>5.880054663331677</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>7.900702181510525</v>
+        <v>7.914159475220742</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>7.935085338855956</v>
+        <v>7.948537627576066</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>7.514830727911054</v>
+        <v>7.528386774262657</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>8.262064497998296</v>
+        <v>8.251634862300143</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>328</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>4.823634850521728</v>
+        <v>4.836157140197351</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>7.480353920484305</v>
+        <v>7.493263730060356</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>7.085485213887715</v>
+        <v>7.098492345305317</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>9.045006639178141</v>
+        <v>9.057985781576605</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>6.982195180203533</v>
+        <v>6.995305984578472</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>7.889393215480169</v>
+        <v>7.902436111774534</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>9.633927790890816</v>
+        <v>9.646994045191292</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>8.252110245767852</v>
+        <v>8.26529125506309</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>8.191110359585551</v>
+        <v>8.204309098540314</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>8.255619320899086</v>
+        <v>8.269024448551917</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>10.7947684356059</v>
+        <v>10.80822572931612</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>11.13402964173181</v>
+        <v>11.14748193045192</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>10.40889698200643</v>
+        <v>10.42245302835803</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>10.35374026550222</v>
+        <v>10.34331062980407</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>266</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>5.777238371519353</v>
+        <v>5.789760661194975</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>6.797243705923513</v>
+        <v>6.810153515499564</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>7.906134397823166</v>
+        <v>7.919141529240768</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>9.916086778550969</v>
+        <v>9.929065920949434</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>7.497966315358497</v>
+        <v>7.511077119733436</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>9.675107501194461</v>
+        <v>9.688150397488826</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>10.34225348317029</v>
+        <v>10.35531973747077</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>9.875070084388788</v>
+        <v>9.888251093684026</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>10.94188974707867</v>
+        <v>10.95508848603343</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>11.59552396054698</v>
+        <v>11.60892908819982</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>11.3907706362294</v>
+        <v>11.40422792993962</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>11.8010936431989</v>
+        <v>11.81454593191901</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>12.13271873150212</v>
+        <v>12.14627477785372</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>12.75837991340246</v>
+        <v>12.74795027770431</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>201</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.232929838993996</v>
+        <v>2.245452128669619</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>6.093993041950149</v>
+        <v>6.1069028515262</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>8.684198962219227</v>
+        <v>8.697206093636829</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>10.80450184607052</v>
+        <v>10.81748098846898</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>8.773543317565505</v>
+        <v>8.786654121940444</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>11.55854744433589</v>
+        <v>11.57159034063025</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>11.97132616487455</v>
+        <v>11.98439241917502</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>11.50414276609305</v>
+        <v>11.51732377538828</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>13.43319263115453</v>
+        <v>13.4463913701093</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>13.08057988393755</v>
+        <v>13.09398501159038</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>13.87085143524187</v>
+        <v>13.88430872895209</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>14.40274703039825</v>
+        <v>14.41619931911836</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>15.97254217069712</v>
+        <v>15.98609821704872</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>16.22226350297341</v>
+        <v>16.21183386727525</v>
       </c>
     </row>
     <row r="32">
@@ -3569,98 +3569,98 @@
         <v>164</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-1.883682222649</v>
+        <v>-1.871159932973377</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>3.212061237557471</v>
+        <v>3.224971047133522</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>6.47572911632674</v>
+        <v>6.488736247744342</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>7.82549444405619</v>
+        <v>7.838473586454654</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>7.287073228984021</v>
+        <v>7.30018403335896</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>10.02353955694359</v>
+        <v>10.03658245323795</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>9.329049742110335</v>
+        <v>9.342115996410811</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>8.861866343328835</v>
+        <v>8.875047352624073</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>11.84964694495141</v>
+        <v>11.86284568390617</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>10.99952175992348</v>
+        <v>11.01292688757631</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>13.23379282584979</v>
+        <v>13.24725011956001</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>13.26817598319522</v>
+        <v>13.28162827191533</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>15.28694576249423</v>
+        <v>15.30050180884584</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>15.53666709477052</v>
+        <v>15.52623745907237</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.09628</t>
+          <t>X &gt; 0.09627</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>130</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-4.031899858671515</v>
+        <v>-4.019377568995893</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>2.048834220671921</v>
+        <v>2.061744030247972</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>7.038580898690718</v>
+        <v>7.05158803010832</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>4.861141723605911</v>
+        <v>4.874120866004375</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>5.091951277764508</v>
+        <v>5.105062082139447</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>8.466316292403242</v>
+        <v>8.479359188697607</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>9.15081334436173</v>
+        <v>9.163879598662206</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>7.914399176349463</v>
+        <v>7.9275801856447</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>8.622630059397927</v>
+        <v>8.635828798352691</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>7.77250487437</v>
+        <v>7.785910002022831</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>11.41390539620627</v>
+        <v>11.42736268991649</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>12.21751932278248</v>
+        <v>12.23097161150259</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>13.33572625029911</v>
+        <v>13.34928229665071</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>14.35467835180617</v>
+        <v>14.34424871610802</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>100</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-4.493438320209975</v>
+        <v>-4.480916030534353</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>2.894988066825761</v>
+        <v>2.907897876401812</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>7.500119360229178</v>
+        <v>7.51312649164678</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3.630372492836671</v>
+        <v>3.643351635235135</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>4.091951277764508</v>
+        <v>4.105062082139447</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>7.389393215480169</v>
+        <v>7.402436111774534</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>9.30465949820789</v>
+        <v>9.317725752508366</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>7.837476099426389</v>
+        <v>7.850657108721627</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>7.776476213244088</v>
+        <v>7.789674952198851</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>6.92635102821616</v>
+        <v>6.939756155868992</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>9.721597703898581</v>
+        <v>9.735054997608799</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>11.75598086124401</v>
+        <v>11.76943314996412</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>12.33572625029911</v>
+        <v>12.34928229665071</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>11.5854475825754</v>
+        <v>11.57501794687725</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-6.064866891638545</v>
+        <v>-6.052344601962922</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>1.847369019206724</v>
+        <v>1.860278828782775</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>8.595357455467273</v>
+        <v>8.608364586884875</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>5.154182016646203</v>
+        <v>5.167161159044667</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>4.615760801574034</v>
+        <v>4.628871605948973</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>8.484631310718264</v>
+        <v>8.497674207012629</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>9.590373783922182</v>
+        <v>9.603440038222658</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>6.742238004188295</v>
+        <v>6.755419013483532</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>6.681238118005993</v>
+        <v>6.694436856960756</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>5.831112932978066</v>
+        <v>5.844518060630897</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>9.197788180089063</v>
+        <v>9.211245473799281</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>10.42264752791067</v>
+        <v>10.43609981663078</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>11.19286910744197</v>
+        <v>11.20642515379357</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>10.25211424924206</v>
+        <v>10.2416846135439</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that MA Ratio-7 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that MA Ratio-7 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3904,989 +3904,989 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.1018</t>
+          <t>X &lt; -0.1017</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>12.98275215598051</v>
+        <v>12.99527444565613</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>6.609273781111476</v>
+        <v>6.622183590687527</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>12.16678602689583</v>
+        <v>12.17979315831344</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>11.10656296902716</v>
+        <v>11.11954211142562</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>6.996713182526413</v>
+        <v>7.009823986901353</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1512979773849352</v>
+        <v>0.1643408736793006</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>2.447516641065029</v>
+        <v>2.460582895365505</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>5.551761813712098</v>
+        <v>5.564942823007335</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>1.919333356101227</v>
+        <v>1.93253209505599</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>7.021589123454255</v>
+        <v>7.034994251107086</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>4.435883418184289</v>
+        <v>4.449340711894507</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>5.660742766005917</v>
+        <v>5.674195054726027</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>6.430964345537205</v>
+        <v>6.444520391888808</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>5.490209487337303</v>
+        <v>5.479779851639151</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.09444</t>
+          <t>X &lt; -0.09441</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>105</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>9.41132358455193</v>
+        <v>9.423845874227553</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3.037845209682906</v>
+        <v>3.050755019258958</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>8.357262217372032</v>
+        <v>8.370269348789634</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>8.487515349979532</v>
+        <v>8.500494492377996</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>4.139570325383559</v>
+        <v>4.152681129758498</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-2.229654403567444</v>
+        <v>-2.216611507273079</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1.49513568868408</v>
+        <v>1.508201942984556</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>4.837476099426389</v>
+        <v>4.850657108721627</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.01457145133932869</v>
+        <v>0.02777019029409189</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>4.878731980597117</v>
+        <v>4.892137108249948</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>1.816835799136683</v>
+        <v>1.830293092846901</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>1.851218956482114</v>
+        <v>1.864671245202224</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>4.288107202680067</v>
+        <v>4.30166324903167</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>4.537828534956354</v>
+        <v>4.527398899258202</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.0871</t>
+          <t>X &lt; -0.08708</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>131</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>10.10198152711828</v>
+        <v>10.1145038167939</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>3.910255242398286</v>
+        <v>3.923165051974337</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>7.332180428931473</v>
+        <v>7.345187560349075</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>5.172357225661102</v>
+        <v>5.185336368059566</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.81714211745917</v>
+        <v>0.8302529218341093</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-2.702209837954946</v>
+        <v>-2.689166941660581</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-1.260225997975319</v>
+        <v>-1.247159743674843</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>2.089384496372951</v>
+        <v>2.102565505668188</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-1.025050504313164</v>
+        <v>-1.011851765358401</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>1.178259425162722</v>
+        <v>1.191664552815553</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.553211456406757</v>
+        <v>-0.5397541626965392</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-1.282187077687283</v>
+        <v>-1.268734788967173</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.5876346472456717</v>
+        <v>0.6011906935972746</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>2.364073536773873</v>
+        <v>2.353643901075721</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.07977</t>
+          <t>X &lt; -0.07974</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>7.633143958271035</v>
+        <v>7.267511642421617</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>3.489924775686525</v>
+        <v>3.769533096527603</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>3.727967461494998</v>
+        <v>4.003692529382626</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>3.225309201697435</v>
+        <v>3.504986855360926</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.1552424170050202</v>
+        <v>0.450974031824984</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-3.344783999709712</v>
+        <v>-3.654167661810369</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-2.163694932171857</v>
+        <v>-2.481016385856414</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.09923276133309855</v>
+        <v>-0.4323617592029052</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-2.058966824730604</v>
+        <v>-2.380136368555867</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.2554649522667916</v>
+        <v>-0.08540107683541009</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-1.215111156860907</v>
+        <v>-0.9190330527056645</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.5478166071104198</v>
+        <v>-0.2557240827402794</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.9306629591598679</v>
+        <v>0.5819866991664355</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>1.180384291436155</v>
+        <v>0.8077223493929679</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.07243</t>
+          <t>X &lt; -0.07241</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>206</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>5.273551971052157</v>
+        <v>5.28607426072778</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.2215167875431661</v>
+        <v>-0.2086069779671149</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1.810798971879663</v>
+        <v>1.823806103297265</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.970178318079391</v>
+        <v>0.9831574604778552</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.0536797901966608</v>
+        <v>-0.04056898582172153</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-3.154296104908184</v>
+        <v>-3.141253208613819</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-3.724466715384345</v>
+        <v>-3.711400461083869</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.3081549685347795</v>
+        <v>-0.2949739592395417</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-1.825465534328728</v>
+        <v>-1.812266795373965</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.7338431465411261</v>
+        <v>-0.7204380188882951</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-2.394907150470353</v>
+        <v>-2.381449856760135</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-2.360523993124922</v>
+        <v>-2.347071704404811</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-1.809904817662058</v>
+        <v>-1.796348771310456</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-2.045620378589653</v>
+        <v>-2.056050014287806</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.0651</t>
+          <t>X &lt; -0.06507</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>253</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>5.214071561212947</v>
+        <v>5.22659385088857</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.8356995292763685</v>
+        <v>0.8486093388524196</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.021858490663959</v>
+        <v>2.034865622081561</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>3.3378823742596</v>
+        <v>3.350861516658064</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.61369040819929</v>
+        <v>1.626801212574229</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-2.041436824045526</v>
+        <v>-2.028393927751161</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-2.126170541317805</v>
+        <v>-2.113104287017329</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.9639583128651239</v>
+        <v>0.9771393221603617</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.2828123243053113</v>
+        <v>-0.2696135853505481</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.4480901586509418</v>
+        <v>0.4614952863037729</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.5471769996587312</v>
+        <v>-0.5337197059485135</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.9080507593093472</v>
+        <v>-0.8945984705892371</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.933048453258202</v>
+        <v>-0.9194924069065991</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.473840954974001</v>
+        <v>-1.484270590672153</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.05776</t>
+          <t>X &lt; -0.05774</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>311</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>5.384375184613177</v>
+        <v>5.396897474288799</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.200454304767895</v>
+        <v>1.213364114343946</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>3.699476273412451</v>
+        <v>3.712483404830053</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>4.472816222740214</v>
+        <v>4.485795365138678</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>2.96976478258766</v>
+        <v>2.982875586962599</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.591314180018216</v>
+        <v>-0.5782712837238506</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.2885823277898751</v>
+        <v>0.3016485820903512</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2.393746195889413</v>
+        <v>2.406927205184651</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.4034858595463362</v>
+        <v>0.4166845985010994</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.4466393254815912</v>
+        <v>-0.4332341978287602</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.3298492414390424</v>
+        <v>-0.3163919477288246</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.6170094924537395</v>
+        <v>-0.6035572037336294</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-2.001894328479025</v>
+        <v>-1.988338282127422</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-3.03834662964325</v>
+        <v>-3.048776265341402</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.05043</t>
+          <t>X &lt; -0.05041</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>4.686718337753469</v>
+        <v>4.810750636132312</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.05801454414028484</v>
+        <v>0.07456454306848315</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.635889595216128</v>
+        <v>1.76312649164678</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2.549432545055993</v>
+        <v>2.674601635235142</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.749914724239709</v>
+        <v>1.875895415472783</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.2196804217464816</v>
+        <v>0.3503527784411986</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.3872465070140336</v>
+        <v>-0.2551909141582982</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.4510531229250816</v>
+        <v>0.5798237753882916</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.437623003466094</v>
+        <v>-1.304075047801149</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-2.026651582749892</v>
+        <v>-1.893577177464344</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.970308301323342</v>
+        <v>-1.837861669057865</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-2.19702174972204</v>
+        <v>-2.063900183369213</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.878372966411071</v>
+        <v>-2.744467703349287</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-4.195231268599528</v>
+        <v>-4.081232053122754</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.04309</t>
+          <t>X &lt; -0.04307</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>466</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>5.017291293523925</v>
+        <v>5.029813583199548</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.259794933778558</v>
+        <v>1.272704743354609</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.937887600572523</v>
+        <v>1.950894731990125</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.711917557214356</v>
+        <v>2.72489669961282</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2.388088616820305</v>
+        <v>2.401199421195244</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.7542000824329591</v>
+        <v>0.7672429787273245</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.1889027335517639</v>
+        <v>-0.1758364792512879</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.4168752410572907</v>
+        <v>0.4300562503525285</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.9316782931936842</v>
+        <v>-0.918479554238921</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.425580302255945</v>
+        <v>-2.412175174603114</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.201149077217295</v>
+        <v>-2.187691783507077</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-2.166765919871864</v>
+        <v>-2.153313631151754</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-2.801612805494884</v>
+        <v>-2.788056759143281</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-3.624852846609151</v>
+        <v>-3.635282482307304</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.03576</t>
+          <t>X &lt; -0.03574</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>3.38390409887009</v>
+        <v>3.301396894635708</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.7501839782397326</v>
+        <v>0.6698026383065852</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>3.081039292086075</v>
+        <v>2.996119688925688</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.870576922138213</v>
+        <v>2.786208778092281</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>3.183944463454459</v>
+        <v>3.268327388261895</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.777808888393288</v>
+        <v>1.69495311857726</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.1808600929335071</v>
+        <v>-0.09043751279775591</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.5444607672287702</v>
+        <v>0.6329700338916879</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.1427453784911066</v>
+        <v>0.2318518229471422</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.218453060369875</v>
+        <v>-1.128271055015361</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.423206384687454</v>
+        <v>-1.503040240486435</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.070254232452754</v>
+        <v>-2.14893419697465</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.320151092119971</v>
+        <v>-2.399017023077178</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.581503013676738</v>
+        <v>-2.513417427272415</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.02842</t>
+          <t>X &lt; -0.0284</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>736</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2.126126897181337</v>
+        <v>2.138649186856959</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.7862924146518537</v>
+        <v>0.7992022242279049</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.61424979501178</v>
+        <v>1.627256926429382</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2.423850753706247</v>
+        <v>2.436829896104712</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>2.428907799503641</v>
+        <v>2.44201860387858</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.367654085045388</v>
+        <v>1.380696981339753</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.01118123733832</v>
+        <v>1.024247491638796</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.6798674037742174</v>
+        <v>0.6930484130694552</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.3471283871571345</v>
+        <v>0.3603271261118977</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.9106054935229722</v>
+        <v>-0.8972003658701411</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.4360109917535908</v>
+        <v>-0.4225536980433731</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.896193051799472</v>
+        <v>-1.882740763079362</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.180578097526976</v>
+        <v>-2.167022051175373</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.79498720003329</v>
+        <v>-1.805416835731442</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.02109</t>
+          <t>X &lt; -0.02107</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.510890684119026</v>
+        <v>1.573138023519704</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.7651179369556402</v>
+        <v>0.8268167953207453</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.560725420835233</v>
+        <v>1.621234599754892</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.015653878118059</v>
+        <v>2.075784067667577</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.477232663045889</v>
+        <v>1.537494514571883</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.402394298903786</v>
+        <v>1.402436111774541</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.9926334960410443</v>
+        <v>1.053656488439103</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.5254500972595437</v>
+        <v>0.5865878446523638</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.03108076362327949</v>
+        <v>0.09270525522914852</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.8190444214046479</v>
+        <v>-0.757213541100711</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.2654012126778014</v>
+        <v>-0.2043389417851458</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.20609931210376</v>
+        <v>-1.143986763455793</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.301326837458205</v>
+        <v>-1.239462292093876</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.8349207814549402</v>
+        <v>-0.797276425417131</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.01375</t>
+          <t>X &lt; -0.01374</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1192</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.648821094015972</v>
+        <v>1.616073936020832</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.7067035479973214</v>
+        <v>0.7196133575733725</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2.116534770614436</v>
+        <v>2.082164148550547</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.74427534040786</v>
+        <v>1.757254482806324</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.169067790756962</v>
+        <v>1.135212835908298</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.177983819507013</v>
+        <v>1.144263437843271</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.5060017800870824</v>
+        <v>0.5190680343875584</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.1289668535937452</v>
+        <v>-0.1157858442985074</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.1899667397760467</v>
+        <v>-0.1767680008212835</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.9561993073543107</v>
+        <v>-0.9427941797014796</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.8253821618732289</v>
+        <v>-0.8119248681630111</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.62992517902444</v>
+        <v>-1.61647289030433</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.630716702721024</v>
+        <v>-1.617160656369421</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.7937470482970923</v>
+        <v>-0.8041766839952444</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.006416</t>
+          <t>X &lt; -0.006402</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1527</v>
+        <v>1530</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.161914160207772</v>
+        <v>1.134719148618743</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.007259607295736714</v>
+        <v>0.07999696375513565</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2.195089967675294</v>
+        <v>2.097220363876247</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.100960728130794</v>
+        <v>2.003429913121636</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.926483651865226</v>
+        <v>1.828299680050669</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.541225676213159</v>
+        <v>1.444238855079561</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.9983767756948012</v>
+        <v>1.004000262312289</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.3348582983792738</v>
+        <v>0.3408531871530016</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.2738584121969723</v>
+        <v>0.2798710306302254</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.7071568251869849</v>
+        <v>-0.7007667199479997</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.9119101495045641</v>
+        <v>-0.9054678782081922</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.59742228011725</v>
+        <v>-1.590043974218887</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.690451760172095</v>
+        <v>-1.683397441911374</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.273753465230755</v>
+        <v>-1.261583360312294</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 0.0009193</t>
+          <t>X &lt; 0.0009315</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.8804835468625711</v>
+        <v>0.8659399532384739</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.05742461504911489</v>
+        <v>0.04285475108472525</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.213679543063101</v>
+        <v>1.198405679464038</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.626307452186268</v>
+        <v>1.61084782619502</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.421386966630799</v>
+        <v>1.405875090269525</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.391427803476098</v>
+        <v>1.375999914519831</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.8771785821773506</v>
+        <v>0.8619780414198672</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.4608857686375885</v>
+        <v>0.4740667779328263</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.6543388086639368</v>
+        <v>0.6675375476187</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.2975675468474535</v>
+        <v>-0.2841624191946224</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.4514302859232942</v>
+        <v>-0.4379729922130764</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.7223906400282516</v>
+        <v>-0.7089383513081415</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.04086408048969</v>
+        <v>-1.027308034138088</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.7628212565284684</v>
+        <v>-0.7506817986698309</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.008254</t>
+          <t>X &lt; 0.008265</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2377</v>
+        <v>2379</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.1911254381792844</v>
+        <v>0.2013974648554253</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.1394223402241721</v>
+        <v>-0.1298379726547836</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.7478103761821586</v>
+        <v>0.756415082250804</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.859267914928239</v>
+        <v>0.8678585592804637</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.848253798772916</v>
+        <v>0.8565314356239071</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.9589602604570544</v>
+        <v>0.9673248140004915</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.8975947379051163</v>
+        <v>0.9059610466260182</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.4304113391236157</v>
+        <v>0.4622586219624907</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.1591507296444163</v>
+        <v>0.1911041241198319</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.3545572981084817</v>
+        <v>-0.3225389260982254</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.3911020437885497</v>
+        <v>-0.3591022113025133</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.029553200993163</v>
+        <v>-0.9972755511708087</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.029286365344284</v>
+        <v>-0.9970817218444523</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.9665086647952421</v>
+        <v>-0.9394839446738246</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.01559</t>
+          <t>X &lt; 0.0156</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2696</v>
+        <v>2697</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.04078291545410195</v>
+        <v>0.03387686887392505</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.4410593054910308</v>
+        <v>-0.4480029745045755</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.2205932587852644</v>
+        <v>0.2133485493817986</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.2970391595033419</v>
+        <v>0.2897788844021179</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.9644966649449458</v>
+        <v>0.9569139339913022</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.023196032381584</v>
+        <v>1.015626182170976</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.14448152267952</v>
+        <v>1.13685103049206</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.6772981238980194</v>
+        <v>0.6904791331932572</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.5792200026397154</v>
+        <v>0.5924187415944786</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.09987716837188998</v>
+        <v>0.1132822960247211</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.1048761559456892</v>
+        <v>-0.09141886223547147</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.5895882896644054</v>
+        <v>-0.5761360009442953</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.4907476095451599</v>
+        <v>-0.477191563193557</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.3314663640121367</v>
+        <v>-0.3256123831190436</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.02292</t>
+          <t>X &lt; 0.02293</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2982</v>
+        <v>2983</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.2207110474827019</v>
+        <v>-0.2256537518841668</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.5443298870358149</v>
+        <v>-0.5493213749350829</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.0486143435067703</v>
+        <v>0.04338393063039803</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.1302052128099191</v>
+        <v>0.1249569864057136</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.5136380247524599</v>
+        <v>0.5082069466426233</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.6287638214393283</v>
+        <v>0.6233196459110815</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.5625295584892029</v>
+        <v>0.5570963584675255</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.3148630340997585</v>
+        <v>0.3094648783130509</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.2873639854383967</v>
+        <v>0.3005627243931599</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.1272503118173418</v>
+        <v>-0.1138451841645107</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.4473031003909682</v>
+        <v>-0.4525496925084553</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.6288666077469358</v>
+        <v>-0.6340521047275658</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.5797950369955558</v>
+        <v>-0.5662389906439529</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.6130768976392176</v>
+        <v>-0.608689729958158</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.03026</t>
+          <t>X &lt; 0.03027</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3218</v>
+        <v>3220</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.4030078463790687</v>
+        <v>-0.4227297105095928</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.4804766171890975</v>
+        <v>-0.5007708542483442</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.3319227841773937</v>
+        <v>-0.3524665712209796</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.1538804519866304</v>
+        <v>-0.1435132966112107</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.1307109676869871</v>
+        <v>0.1097103622757984</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.1660681534454298</v>
+        <v>0.1451515488483111</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.05680497588456745</v>
+        <v>-0.0776230847009387</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.1035543164643613</v>
+        <v>-0.0935116257696933</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.0404077097850859</v>
+        <v>-0.01330363917564625</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.3318736769359205</v>
+        <v>-0.3357635462718704</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.6435063010688253</v>
+        <v>-0.6335456849850658</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.8713483313025705</v>
+        <v>-0.8612310337726896</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.6841557006173176</v>
+        <v>-0.6743128601329005</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.8210160594382714</v>
+        <v>-0.8038640407003967</v>
       </c>
     </row>
     <row r="25">
@@ -4896,101 +4896,101 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3417</v>
+        <v>3418</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.1166520851560264</v>
+        <v>-0.1193999955489318</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.3710562738976861</v>
+        <v>-0.3738169092499746</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.5751651451691302</v>
+        <v>-0.5778886775480885</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.5751149560833468</v>
+        <v>-0.5778330744234523</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.1927202550822145</v>
+        <v>-0.1955800661384259</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.4926161303142251</v>
+        <v>-0.4953741072035598</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.6491821611552453</v>
+        <v>-0.6519004157159287</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.5161182898196657</v>
+        <v>-0.518901757769747</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.6355635295963609</v>
+        <v>-0.6223647906415977</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.6512578580743948</v>
+        <v>-0.6540486366500033</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.9860046352827041</v>
+        <v>-0.9887099833909048</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.198684245512354</v>
+        <v>-1.201327083954006</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.134724305581528</v>
+        <v>-1.137409718558416</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.102875507854804</v>
+        <v>-1.100230736563361</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.04493</t>
+          <t>X &lt; 0.04494</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3556</v>
+        <v>3557</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.2098855042951513</v>
+        <v>-0.2120084675091363</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.4334872694971068</v>
+        <v>-0.4356157128388602</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.6731354757674595</v>
+        <v>-0.675214315528109</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.8082141588739233</v>
+        <v>-0.8102508318240069</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.490096408069995</v>
+        <v>-0.4922458258807438</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.5702027441157895</v>
+        <v>-0.5723184464302307</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.6678355902007596</v>
+        <v>-0.6699285684792926</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.5864430471204969</v>
+        <v>-0.5885794896505274</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.5759528797073301</v>
+        <v>-0.5780959630173115</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.7365703200984512</v>
+        <v>-0.7387049505617895</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.038166274747105</v>
+        <v>-1.040225901267604</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.213102893674481</v>
+        <v>-1.215113070884435</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.139955503988212</v>
+        <v>-1.142004943371767</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.127713272317742</v>
+        <v>-1.12557243827878</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3679</v>
+        <v>3680</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.3265910829401975</v>
+        <v>-0.3281946657902353</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.4610130168913784</v>
+        <v>-0.4626330011713193</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.6787424283887091</v>
+        <v>-0.6803170195967922</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.7507606055639755</v>
+        <v>-0.7523123214044247</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.5425389608472031</v>
+        <v>-0.5441653507691981</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.6371866597571483</v>
+        <v>-0.6387786387677679</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.5987588414557052</v>
+        <v>-0.600364836046019</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.4813841448069951</v>
+        <v>-0.4830379536766358</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.5003967509252902</v>
+        <v>-0.5020482499721126</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.6568691727069975</v>
+        <v>-0.6585066020028876</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.8737309218482991</v>
+        <v>-0.8753169817558515</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.8786292990385149</v>
+        <v>-0.88021378105163</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.8490563583965383</v>
+        <v>-0.8506633702876201</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.9375206153044644</v>
+        <v>-0.9358516183401449</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3770</v>
+        <v>3771</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.3654975324753664</v>
+        <v>-0.3667511256717688</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.5619130436977642</v>
+        <v>-0.5631568420755784</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.6252443001781245</v>
+        <v>-0.6264821810131878</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.6659238034596129</v>
+        <v>-0.6671482325247027</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.4227351472156471</v>
+        <v>-0.4240384469610845</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.5608450058009353</v>
+        <v>-0.5621047720571681</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.6047924477809872</v>
+        <v>-0.6060434375392845</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.5015069514210708</v>
+        <v>-0.5027980143919564</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.5215370317890233</v>
+        <v>-0.5228250478011489</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.5357581397753677</v>
+        <v>-0.5370650361839893</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.7522957495867075</v>
+        <v>-0.7535512557033357</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.7562142607072033</v>
+        <v>-0.757468519794692</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.7109457200005451</v>
+        <v>-0.7122235357989197</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.7912102423582894</v>
+        <v>-0.7898720027382353</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3844</v>
+        <v>3845</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.4322508688228837</v>
+        <v>-0.4332229252984803</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.6039745887758912</v>
+        <v>-0.6049359322577601</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.6218002247254262</v>
+        <v>-0.6227656245357949</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.7629850577601047</v>
+        <v>-0.7639116591876842</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.5867406506030051</v>
+        <v>-0.587724632961752</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.6386441676974002</v>
+        <v>-0.6396090478413541</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.7612973961052774</v>
+        <v>-0.7622327106276643</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.6430433810930865</v>
+        <v>-0.6440195986271107</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.6119363614506383</v>
+        <v>-0.6129224503985498</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.6162685144033802</v>
+        <v>-0.6172716435594339</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.8326003725246096</v>
+        <v>-0.8335520709982731</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.8618038501444403</v>
+        <v>-0.8627477702334403</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.7995143218725431</v>
+        <v>-0.8004836939889088</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.795405695260186</v>
+        <v>-0.7942928463607259</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3906</v>
+        <v>3907</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.4138261742543747</v>
+        <v>-0.4145894999221014</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.4296673696214057</v>
+        <v>-0.4304537439094815</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.5555354776569601</v>
+        <v>-0.5562966834425467</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.6668695909222606</v>
+        <v>-0.6676006241470347</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.5019184540362573</v>
+        <v>-0.5027009413539147</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.6249143982142584</v>
+        <v>-0.6256609508052833</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.6447399395636424</v>
+        <v>-0.6454832408488045</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.6124216510848584</v>
+        <v>-0.6131813783726727</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.6594736716958209</v>
+        <v>-0.6602227983123967</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.7028049820140154</v>
+        <v>-0.7035575746347149</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.6887374201740712</v>
+        <v>-0.6894974320587224</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.7168952902401173</v>
+        <v>-0.7176479449450639</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.7390114000720232</v>
+        <v>-0.7397658097976034</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.7821919463544518</v>
+        <v>-0.781265646672793</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3971</v>
+        <v>3972</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.1340005692059663</v>
+        <v>-0.134617410710014</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.2762396509748868</v>
+        <v>-0.2768410794214731</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.4566862650847341</v>
+        <v>-0.4572475982352131</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.5389317020892221</v>
+        <v>-0.5394710669245768</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.435686913190267</v>
+        <v>-0.4362591939218419</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.5517980386037777</v>
+        <v>-0.5523377575721966</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.5475275304497274</v>
+        <v>-0.5480696734780679</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.5233486428416541</v>
+        <v>-0.5239029717208084</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.5957571871583269</v>
+        <v>-0.5962943714119149</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.5767936258718862</v>
+        <v>-0.577346459825165</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.6166005849791247</v>
+        <v>-0.6171462602528379</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.6437170999943476</v>
+        <v>-0.6442558283952096</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.7226826117351237</v>
+        <v>-0.7232070061431486</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.7358820573137947</v>
+        <v>-0.7351532515114769</v>
       </c>
     </row>
     <row r="32">
@@ -5260,101 +5260,101 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4008</v>
+        <v>4009</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.05567881483106163</v>
+        <v>0.05513568503003796</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.1000368087961263</v>
+        <v>-0.1005577316558757</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.282413608170927</v>
+        <v>-0.2828934088507324</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.3128828580841727</v>
+        <v>-0.3133540129360526</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.2901746868857273</v>
+        <v>-0.2906571811756322</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.3775390554361664</v>
+        <v>-0.3779970472994094</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.3242321580810241</v>
+        <v>-0.3247045263760953</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.3045268901102318</v>
+        <v>-0.3050091428350328</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.4016947311865096</v>
+        <v>-0.4021536477015033</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.3657726008965057</v>
+        <v>-0.3662493263139197</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.4569113960764923</v>
+        <v>-0.4573677341957847</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.4584829791549865</v>
+        <v>-0.4589388270989545</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.5405521233601647</v>
+        <v>-0.5409920175637453</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.5512789643307912</v>
+        <v>-0.5506991895657549</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.09628</t>
+          <t>X &lt; 0.09627</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4042</v>
+        <v>4043</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.1082879436617858</v>
+        <v>0.1078413659153483</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.03495766578399895</v>
+        <v>-0.03538202495452936</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.2437740520580149</v>
+        <v>-0.2441502720433988</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.149489303806952</v>
+        <v>-0.149887940387849</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.156135614360899</v>
+        <v>-0.1565371281270842</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.2402364141494644</v>
+        <v>-0.2406149867196703</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.2374496645483504</v>
+        <v>-0.237829803047191</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.1971088808107666</v>
+        <v>-0.1975029307943004</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.1951076760566295</v>
+        <v>-0.1955029134137973</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.1665802619469687</v>
+        <v>-0.1669895817144038</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.2833466718739786</v>
+        <v>-0.2837289865731094</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.3093010378657723</v>
+        <v>-0.3096768623968202</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.344709070007589</v>
+        <v>-0.3450797211534393</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.3779368805616556</v>
+        <v>-0.3774925651187999</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4072</v>
+        <v>4073</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.08918101883531193</v>
+        <v>0.08883433657283746</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.04036942582849434</v>
+        <v>-0.04069453485889341</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2015705736429823</v>
+        <v>-0.2018588168742781</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.08251334743769689</v>
+        <v>-0.08283009388559748</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.09305239780520225</v>
+        <v>-0.09337005896785655</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.1498224707943479</v>
+        <v>-0.1501245351257268</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.1721730587913797</v>
+        <v>-0.1724703259230083</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.1355498937074984</v>
+        <v>-0.1358591942938148</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.1094693349531184</v>
+        <v>-0.1097855676638275</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.0873879315483066</v>
+        <v>-0.0877150239200688</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.1557029095983467</v>
+        <v>-0.1560146785442953</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.2057275334540734</v>
+        <v>-0.2060269727352591</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.2193928265484288</v>
+        <v>-0.2196916846944035</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.2013893525915975</v>
+        <v>-0.2010684759069434</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4088</v>
+        <v>4089</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.1034892584293772</v>
+        <v>0.1031892839463922</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.00745095756447256</v>
+        <v>-0.007732457663038872</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.1939523645817474</v>
+        <v>-0.194190581523948</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.09925171409353339</v>
+        <v>-0.09951247796320217</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.08744828288962481</v>
+        <v>-0.0877148822334135</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.1428333470198311</v>
+        <v>-0.1430850012349865</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.1410059474575576</v>
+        <v>-0.1412586224916339</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.08191813604014442</v>
+        <v>-0.08218782412330228</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.05616488130758768</v>
+        <v>-0.05644131550999276</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.03748083884151754</v>
+        <v>-0.03776644369123261</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.106317231325086</v>
+        <v>-0.1065872311302059</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.1315497011031752</v>
+        <v>-0.1318134889994553</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.1467878118187613</v>
+        <v>-0.1470502216866976</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.127859658129104</v>
+        <v>-0.1275988298407853</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/ma/ma_ratio_7.xlsx
+++ b/workspaces/btc_daily_14days/ma/ma_ratio_7.xlsx
@@ -568,1197 +568,1197 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.09806</t>
+          <t>X ≈ -0.09775</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-4.847294764629552</v>
+        <v>-2.503042527404844</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-11.2022248852123</v>
+        <v>-8.613705466076361</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-6.85002615644423</v>
+        <v>-4.475673455539997</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-1.971394359155596</v>
+        <v>0.1873107061570849</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-7.260130097664266</v>
+        <v>-4.836021903933585</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-11.7173234986883</v>
+        <v>-9.1011535680218</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-2.297359698850265</v>
+        <v>-0.08864871493575777</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1.990493217627666</v>
+        <v>3.984864438418782</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-7.581907750296608</v>
+        <v>-5.130728709655038</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-3.675738326576131</v>
+        <v>-1.414117885565794</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-8.639532562513025</v>
+        <v>-10.7026261688878</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-13.36686901200417</v>
+        <v>-15.19034739896372</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-4.268728086069821</v>
+        <v>-6.500446972332554</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.7178750897343846</v>
+        <v>-1.70752874809741</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.09074</t>
+          <t>X ≈ -0.09044</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>12.86148695419278</v>
+        <v>11.45227775222041</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>7.424175861161679</v>
+        <v>5.889099960298473</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3.196101108189119</v>
+        <v>1.508217689097556</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-8.183082709010243</v>
+        <v>-10.33220057094852</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-12.55950245980338</v>
+        <v>-14.81374534203476</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-4.588307657838008</v>
+        <v>-6.560506209441385</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-12.35315890710817</v>
+        <v>-14.60902304627986</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-8.98226478784715</v>
+        <v>-11.08380621042192</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-5.203788180569184</v>
+        <v>-7.128191020217734</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-13.73899839051456</v>
+        <v>-15.94521599762278</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-10.10357339706923</v>
+        <v>-8.158963214290878</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-13.91597164226661</v>
+        <v>-12.10087666018533</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-14.33948457036647</v>
+        <v>-12.49894862116867</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-6.424982053120999</v>
+        <v>-4.252983293557911</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.08341</t>
+          <t>X ≈ -0.08312</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-6.033928965638651</v>
+        <v>-5.825737256014939</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>3.041375574067587</v>
+        <v>2.565439833380289</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-11.59864563328792</v>
+        <v>-11.12397406788762</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-4.346222273728451</v>
+        <v>-4.346737683337224</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-1.320592319920543</v>
+        <v>-4.835621441720022</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-8.152508167352941</v>
+        <v>-7.891014640393941</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-8.239165961329974</v>
+        <v>-11.28113516198264</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-12.27386988926405</v>
+        <v>-11.74925771166097</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-8.770685740876075</v>
+        <v>-8.459748063293354</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-6.054166397779781</v>
+        <v>-5.954934788613599</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-2.691429459164453</v>
+        <v>-2.829521074107831</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>4.481547952025146</v>
+        <v>3.891254928950751</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.4920329521522433</v>
+        <v>0.1646123565605251</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-6.424982053122754</v>
+        <v>-6.252983293554571</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.07608</t>
+          <t>X ≈ -0.0758</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-1.413463869772634</v>
+        <v>-1.395437057403434</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-13.6257097834909</v>
+        <v>-14.05125072908937</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-5.535841989220451</v>
+        <v>-5.583179642647657</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-7.529490149276249</v>
+        <v>-7.671516924049733</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-1.699616481889656</v>
+        <v>0.707595962777205</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-1.402890113856046</v>
+        <v>-1.237428491895024</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-7.859621645953418</v>
+        <v>-5.734965888332063</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.1696621712351103</v>
+        <v>0.4548870727989964</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.1089091895162468</v>
+        <v>0.41818289090984</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-2.865777048410202</v>
+        <v>-2.624837568683915</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-7.323145677284828</v>
+        <v>-7.270575158029935</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-9.417260953205307</v>
+        <v>-9.435413566812997</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-9.839711143142715</v>
+        <v>-9.832874942155975</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-11.74413098929297</v>
+        <v>-11.80853884911266</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.06874</t>
+          <t>X ≈ -0.06848</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4.948503355971148</v>
+        <v>5.803057680962311</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>5.46576291925696</v>
+        <v>6.304256513638407</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2.951336614305362</v>
+        <v>1.757738346384215</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>13.69341269841103</v>
+        <v>14.3562148555898</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>8.91440435663138</v>
+        <v>9.714709666856784</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2.843838602696309</v>
+        <v>1.673380180739024</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>4.883918597498138</v>
+        <v>3.692932153642523</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>6.542882515510698</v>
+        <v>5.308574411051126</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>6.483758772714019</v>
+        <v>7.353796188775476</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>5.636257102061734</v>
+        <v>6.532573077570746</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>7.559216764714712</v>
+        <v>8.412029710563559</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>5.468876088533193</v>
+        <v>4.307705830331599</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.923050348348717</v>
+        <v>1.830882689198035</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>1.021826457515552</v>
+        <v>-0.002983293556091837</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.06141</t>
+          <t>X ≈ -0.06116</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>6.117975129432097</v>
+        <v>2.480323276283016</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2.79569159620619</v>
+        <v>2.565316509968717</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>10.99861492777581</v>
+        <v>10.48279236504841</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>9.411544131158379</v>
+        <v>7.29011759604672</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>8.877251295050336</v>
+        <v>8.466990919707058</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>5.735720266205497</v>
+        <v>7.078788782924867</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>10.81571533102174</v>
+        <v>12.01104848843509</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>8.63034600036633</v>
+        <v>6.556416601946324</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>3.406086629940539</v>
+        <v>-0.1367810174996151</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-4.331561608885025</v>
+        <v>-7.619648214011683</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.6312099824948021</v>
+        <v>-2.829430862348509</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.6657145568685934</v>
+        <v>-1.106221283715037</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-6.648958258479979</v>
+        <v>-8.166545786330296</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-9.873257915191722</v>
+        <v>-11.25298329355609</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.05407</t>
+          <t>X ≈ -0.05384</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>73</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2.304137583362319</v>
+        <v>5.005588923273585</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-4.762158248776316</v>
+        <v>-4.763402421677938</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-6.523649193307598</v>
+        <v>-5.157884885337836</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-5.029239701358421</v>
+        <v>-5.029714106404711</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-2.833963105159299</v>
+        <v>-4.152198554917469</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>4.297639496959356</v>
+        <v>2.954558248483217</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-2.622570531401642</v>
+        <v>-3.942024250240507</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-7.192959061766111</v>
+        <v>-5.776049568104881</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-8.623534064774219</v>
+        <v>-7.182287759763206</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-8.106351947718828</v>
+        <v>-6.638669236628182</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-8.313068206838395</v>
+        <v>-6.844443841209291</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-8.280918609229516</v>
+        <v>-6.788137214691623</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-5.964146657761759</v>
+        <v>-4.445989190849865</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-8.479776573670705</v>
+        <v>-6.937914800405409</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.04674</t>
+          <t>X ≈ -0.04652</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>82</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>6.032730837450764</v>
+        <v>4.157784069796989</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>6.861378224981223</v>
+        <v>4.988222208874667</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2.821242267447595</v>
+        <v>0.9454761691644364</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2.951751438320663</v>
+        <v>4.727017906927621</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>4.848945483686187</v>
+        <v>5.450325142782987</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2.71364906243241</v>
+        <v>4.50833593011874</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.1955674510728187</v>
+        <v>2.012256565997184</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.2708522044545205</v>
+        <v>1.542794006691175</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.8863362305420139</v>
+        <v>2.721642844373008</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-4.83521171877225</v>
+        <v>-2.985672315910804</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-3.822604391124912</v>
+        <v>-2.50425011325337</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-2.570482632514967</v>
+        <v>-1.227997379276957</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.991274987165383</v>
+        <v>-0.4042587631322263</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.546933272634945</v>
+        <v>1.064089877175611</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.0394</t>
+          <t>X ≈ -0.0392</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>122</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-3.2910219641929</v>
+        <v>-1.686871550516202</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.628057861827564</v>
+        <v>0.00476825620431498</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>6.966350620244306</v>
+        <v>7.785740196776423</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3.01106844176978</v>
+        <v>3.829095160391056</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>6.563259011141533</v>
+        <v>7.431489631542782</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>5.226700072729471</v>
+        <v>6.070136137117196</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.2354617768581733</v>
+        <v>1.101695021916001</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.405695273171496</v>
+        <v>1.455229563697415</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>4.619582872927168</v>
+        <v>4.693965110626088</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>3.772052123027656</v>
+        <v>3.872236243672255</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.111480163373756</v>
+        <v>1.211287931329743</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-2.13081577741535</v>
+        <v>-2.82642110370324</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.9126349081648328</v>
+        <v>-2.402890992477538</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1.771739258352653</v>
+        <v>0.3043937556242327</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.03207</t>
+          <t>X ≈ -0.03188</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.473689793736042</v>
+        <v>-4.203327521034453</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.308473468576722</v>
+        <v>0.2146791169255096</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-3.800666911738205</v>
+        <v>-4.86592597816783</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.044413554815307</v>
+        <v>-0.7172206937790193</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.8400629005477356</v>
+        <v>-2.551512329500838</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.1312972479319257</v>
+        <v>-1.608985645474796</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>5.441936993191469</v>
+        <v>4.358630087762705</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.9300459146953486</v>
+        <v>1.207107086732151</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.8695700118888254</v>
+        <v>1.168881326188725</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.02113683818074463</v>
+        <v>0.0378698763370835</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>3.867111832774846</v>
+        <v>3.856534079350759</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.8244219951628153</v>
+        <v>-0.401681199502768</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.244808089685812</v>
+        <v>-0.7969588586877876</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.007450379309681</v>
+        <v>1.46513751181304</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.02474</t>
+          <t>X ≈ -0.02456</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.6293041375633024</v>
+        <v>0.629135230600788</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.9364124192835988</v>
+        <v>1.660344251899772</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.602176139692645</v>
+        <v>2.84930480546091</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.6728126886403558</v>
+        <v>1.927690171200382</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.989079507538101</v>
+        <v>-1.211477717972841</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.492602726328919</v>
+        <v>1.992225016006493</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.165948633359562</v>
+        <v>0.8733901339138725</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.1693435665381102</v>
+        <v>-0.3643678939591126</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.9535089741977529</v>
+        <v>-1.696890109905489</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.2085666304451266</v>
+        <v>-0.933714661777401</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.6495229640350644</v>
+        <v>-0.08023257395414873</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.747389334669371</v>
+        <v>1.035645796567749</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>2.39127270137935</v>
+        <v>1.698673205507326</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>3.149486031983628</v>
+        <v>2.477175436602643</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.01741</t>
+          <t>X ≈ -0.01724</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.780841972165085</v>
+        <v>0.9721620563112552</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.3547733386375853</v>
+        <v>0.8538945466223922</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>3.681025203153482</v>
+        <v>3.764653485676433</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.6632380536555047</v>
+        <v>0.5911589312426386</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.2478500237757046</v>
+        <v>-0.2671601901545912</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.251747668512877</v>
+        <v>0.3736714824099749</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.321499778216058</v>
+        <v>-1.157502176474736</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-2.532497691915843</v>
+        <v>-2.360331129826321</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.103869330573197</v>
+        <v>-0.9279261919819959</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.580084345523133</v>
+        <v>-1.020296386574948</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.903650988206742</v>
+        <v>-1.959689643473745</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-3.243028653099131</v>
+        <v>-1.902240769946182</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.918242176633768</v>
+        <v>-2.089405547622768</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.8279671277495311</v>
+        <v>-0.002983293556091837</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.01007</t>
+          <t>X ≈ -0.009912</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.5635194834860116</v>
+        <v>-0.4636829841729053</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.174566689403861</v>
+        <v>-3.210607263830887</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2.151224623261257</v>
+        <v>1.357525146711751</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>2.871592373399366</v>
+        <v>2.656542456637801</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>4.264190576317851</v>
+        <v>3.922233573957691</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2.495322039019577</v>
+        <v>2.149581495744407</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.706660599484479</v>
+        <v>2.382324846319008</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.947108977124778</v>
+        <v>2.209045445350377</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.887040151591243</v>
+        <v>1.587536913332571</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.1532822503537474</v>
+        <v>-0.4050210356751833</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.233462574243752</v>
+        <v>-2.070545685654047</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.495133270033932</v>
+        <v>-2.012290157808486</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.915977258183631</v>
+        <v>-2.407283187764918</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-2.874686195134657</v>
+        <v>-3.913802007006382</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.002735</t>
+          <t>X ≈ -0.002593</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>435</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.07702433681787824</v>
+        <v>-0.3353541934717583</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.08769089316277956</v>
+        <v>-0.5483515094425471</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.963636216123405</v>
+        <v>-2.087619717889801</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.2299317408974488</v>
+        <v>-0.349137968882367</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.07882797927261009</v>
+        <v>-0.3812900806463801</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.135578550117188</v>
+        <v>1.041094683196263</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.363239514520842</v>
+        <v>0.183752345313458</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.9397593256832479</v>
+        <v>0.4058345222382016</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2.026382632859367</v>
+        <v>1.747737199152617</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.179961848508505</v>
+        <v>0.9206891833918505</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.205566089177239</v>
+        <v>0.9456506875294863</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.388907595310819</v>
+        <v>1.692863515021216</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.280236367209497</v>
+        <v>0.8368043206959968</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.046282314693336</v>
+        <v>0.9883960167887409</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.004598</t>
+          <t>X ≈ 0.004727</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>414</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-2.956826900754187</v>
+        <v>-2.390880297581013</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.9487718014060533</v>
+        <v>0.1234992734787781</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.345952099139105</v>
+        <v>-0.7516274589949745</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-2.661676970606521</v>
+        <v>-2.311280876488411</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.753113166279654</v>
+        <v>-1.223203592297708</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.9750104404687505</v>
+        <v>-0.7088721797589699</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.108903108726359</v>
+        <v>1.404384774493913</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.4038037512992076</v>
+        <v>0.6970061203907107</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.065705951369125</v>
+        <v>-1.996971319663963</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.5026656362099686</v>
+        <v>-0.1637950695610115</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.01612750223797121</v>
+        <v>0.3567021640622272</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.362326046776062</v>
+        <v>-1.275952354611498</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.8525458790447686</v>
+        <v>-0.2218349188563806</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.835610072446372</v>
+        <v>-0.9389736317202875</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.01193</t>
+          <t>X ≈ 0.01205</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.219375022717237</v>
+        <v>-1.713609194122469</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.82178918595659</v>
+        <v>-3.611938333445806</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-3.84654385014867</v>
+        <v>-4.64332895442471</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-4.030410661168659</v>
+        <v>-4.198412698412703</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.697394388473718</v>
+        <v>1.344084192381445</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.366809430169624</v>
+        <v>0.9819490762797756</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2.848960103504332</v>
+        <v>2.508594574355868</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>2.386164963991156</v>
+        <v>1.725301496512131</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>3.582338788907123</v>
+        <v>3.910551109597598</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>3.366259285018693</v>
+        <v>3.404182846242932</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.908624415709077</v>
+        <v>2.247661446325921</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>2.57302263370233</v>
+        <v>1.988367866230469</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>3.410888084442021</v>
+        <v>3.815432161888786</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>4.266841846248248</v>
+        <v>4.38193734136447</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.01926</t>
+          <t>X ≈ 0.01937</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>286</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-2.674073253904972</v>
+        <v>-2.852602249035705</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.516007599025464</v>
+        <v>-1.641281729726998</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.554499218600682</v>
+        <v>-1.339294552872431</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.422665074214414</v>
+        <v>-1.559940059940061</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-3.699446765264661</v>
+        <v>-3.797440949143727</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-3.050619972843464</v>
+        <v>-3.175005080674538</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-4.878649472458036</v>
+        <v>-4.98391291815166</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.263281885894493</v>
+        <v>-3.351843580632909</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.43958360671003</v>
+        <v>-3.03916584011936</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.25279381184879</v>
+        <v>-2.814043371983288</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-3.860389395317753</v>
+        <v>-4.416785218120779</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.184825111472755</v>
+        <v>-1.561415683553093</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.403857131002539</v>
+        <v>-2.306223959767259</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-3.278128906269643</v>
+        <v>-4.155081195653999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.0266</t>
+          <t>X ≈ 0.02669</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>237</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-2.908270864054394</v>
+        <v>-2.095796014420415</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.106673878659862</v>
+        <v>0.5250118821776155</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-5.338123957143317</v>
+        <v>-4.927728622934907</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-3.523137496743985</v>
+        <v>-2.880349608197662</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-4.902654635495203</v>
+        <v>-4.635421533959764</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-5.86738807805483</v>
+        <v>-5.628458799950913</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-8.058094432286588</v>
+        <v>-7.798819530526721</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-5.159010962797574</v>
+        <v>-4.88912486474954</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-3.957176063894842</v>
+        <v>-3.660274689076303</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-3.130741159513775</v>
+        <v>-2.796339556811127</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.921833692886381</v>
+        <v>-2.578539076077163</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-3.733108769566051</v>
+        <v>-3.786195123522397</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.044617805026071</v>
+        <v>-2.07164840873606</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-3.260425091097389</v>
+        <v>-3.510367259800816</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.03393</t>
+          <t>X ≈ 0.03401</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>198</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>4.818407574781112</v>
+        <v>4.789038039470206</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.686281311853335</v>
+        <v>2.189433603046133</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-4.255528086490074</v>
+        <v>-3.981976393307036</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-7.653252596505816</v>
+        <v>-7.892496392496454</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-5.164078533132674</v>
+        <v>-4.846391998094781</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-10.91812496591278</v>
+        <v>-10.63421253988191</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-9.997577198047644</v>
+        <v>-9.684767619006337</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-7.440299354718839</v>
+        <v>-7.120297349086734</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-10.52718656303382</v>
+        <v>-10.1875729885265</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-5.845835610854863</v>
+        <v>-5.45584601378593</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-6.769995507441706</v>
+        <v>-6.670087471423031</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-6.735617355086383</v>
+        <v>-6.611920734058138</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-8.670919723551279</v>
+        <v>-8.522230175773423</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-5.919931548072249</v>
+        <v>-5.747932788505558</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.04127</t>
+          <t>X ≈ 0.04133</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-2.501851662980798</v>
+        <v>-2.174199388578202</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.976651626852707</v>
+        <v>-1.950431767185691</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-3.098460429292615</v>
+        <v>-3.058455469786075</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-6.565357587862572</v>
+        <v>-6.5</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-7.81450702447998</v>
+        <v>-7.703534855237642</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-2.489726348733292</v>
+        <v>-2.430749336418749</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.142249124732643</v>
+        <v>-1.062833997072701</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-2.327790609294432</v>
+        <v>-2.242952471741795</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.484166977626117</v>
+        <v>0.5772177762642627</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.822833772188559</v>
+        <v>-3.103753661693574</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-2.308110470017105</v>
+        <v>-2.593608394943956</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.554307857230121</v>
+        <v>-1.821155943293348</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.255034250111919</v>
+        <v>-1.502028155571452</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.748723060316998</v>
+        <v>-1.967269007841843</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.0486</t>
+          <t>X ≈ 0.04865</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>123</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-3.700428225656253</v>
+        <v>-3.729624020008885</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.24657366831363</v>
+        <v>-1.247760454758286</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.8283369229874111</v>
+        <v>-0.8284903129917325</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.9279044807636012</v>
+        <v>0.9274099883855982</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-2.049409462575959</v>
+        <v>-2.000863542810187</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-2.565043563022165</v>
+        <v>-2.541086154072552</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1.415286728118126</v>
+        <v>1.463298407108446</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>2.574234344493945</v>
+        <v>2.623481906887662</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.700244057889904</v>
+        <v>1.7735011676696</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.663333391641352</v>
+        <v>1.762680716935925</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>3.89765662362511</v>
+        <v>3.997564659643785</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>8.810083556468236</v>
+        <v>8.93378017749648</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>7.576924573073484</v>
+        <v>7.725614120851311</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>4.550627702974758</v>
+        <v>4.72262646254142</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.05593</t>
+          <t>X ≈ 0.05597</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.931465481083862</v>
+        <v>-3.047746233489228</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-4.6415526730487</v>
+        <v>-5.706192135849285</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.557082535602824</v>
+        <v>1.426951596266107</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2.786208778092281</v>
+        <v>1.556835637480788</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>4.445721422798719</v>
+        <v>3.218124130937412</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2.545293254631673</v>
+        <v>1.340372015347796</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.8361204013377872</v>
+        <v>-0.8708217082862646</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.303189045124427</v>
+        <v>-1.336654468669536</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.364171201647302</v>
+        <v>-1.373627077806404</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>4.37931659542943</v>
+        <v>4.254157244604428</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>4.17461543716918</v>
+        <v>4.050016797068267</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>4.208993589524503</v>
+        <v>3.032914717228863</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>4.887743835112254</v>
+        <v>3.713025607869405</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>5.113479485338786</v>
+        <v>3.962070469884829</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.06327</t>
+          <t>X ≈ 0.06329</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-3.8322673818857</v>
+        <v>-2.510111824886941</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-2.740750772246869</v>
+        <v>-1.315511132265058</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.4328194542991639</v>
+        <v>-0.3203602316908771</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-5.707999716116205</v>
+        <v>-4.357142857142861</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-8.948991971914602</v>
+        <v>-7.624169775872559</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-4.597563888225466</v>
+        <v>-3.184717590386967</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-8.736328301545683</v>
+        <v>-8.800929235167985</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-7.852045593981117</v>
+        <v>-7.877873106662435</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-5.210325047801149</v>
+        <v>-5.137067938021453</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-4.708892492779661</v>
+        <v>-4.572007629947549</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-4.913593651039854</v>
+        <v>-4.77614807748364</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-6.230566850035878</v>
+        <v>-4.717981340118747</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-5.299366351997939</v>
+        <v>-3.72425037779368</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.019576647717273</v>
+        <v>0.691461150888351</v>
       </c>
     </row>
     <row r="29">
@@ -1771,254 +1771,254 @@
         <v>62</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.7448904210785017</v>
+        <v>0.7156946267258704</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>10.42402690865988</v>
+        <v>10.42284012221523</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.577642620679043</v>
+        <v>3.577489230674722</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>5.320770990073854</v>
+        <v>5.320276497695851</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>4.782481436978159</v>
+        <v>4.831027356743931</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.2411457891938866</v>
+        <v>0.2651031981434997</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>6.608048333153576</v>
+        <v>6.656060012143897</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>1.302270011947485</v>
+        <v>1.351517574341202</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-3.597421821994701</v>
+        <v>-3.524164712215004</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-6.060243844131008</v>
+        <v>-5.960896518836435</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>8.251184029866863</v>
+        <v>8.351092065885538</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>8.285562182222186</v>
+        <v>8.409258803250431</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>3.026701651489425</v>
+        <v>3.175391199267253</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.02663085010306077</v>
+        <v>0.1986296096697231</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.07794</t>
+          <t>X ≈ 0.07793</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>65</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>16.74985320023494</v>
+        <v>16.72065740588231</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>8.984820953324892</v>
+        <v>8.983634166880236</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>5.51312649164678</v>
+        <v>5.512973101642459</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>7.181813173696639</v>
+        <v>7.181318681318636</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>3.566600543677914</v>
+        <v>3.615146463443686</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>3.863974573313001</v>
+        <v>3.887931982262614</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5.317725752508366</v>
+        <v>5.365737431498687</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>4.850657108721627</v>
+        <v>4.899904671115344</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>3.251213413737318</v>
+        <v>3.324470523517014</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>7.016679232792114</v>
+        <v>7.116026558086688</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>3.735054997608749</v>
+        <v>3.834963033627425</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>3.769433149964122</v>
+        <v>3.893129770992367</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.2723592197276332</v>
+        <v>0.4210487675054608</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>2.036556408415713</v>
+        <v>2.208555167982375</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.08528</t>
+          <t>X ≈ 0.08525</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>37</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>20.49205694243859</v>
+        <v>20.46286114808596</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>18.88087084937479</v>
+        <v>18.87968406293013</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>18.48609946461975</v>
+        <v>18.48594607461543</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>24.0217300136136</v>
+        <v>24.0212355212356</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>15.37533235240972</v>
+        <v>15.42387827217549</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>18.37540908474747</v>
+        <v>18.39936649369709</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>23.69610413088664</v>
+        <v>23.74411580987696</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>23.2290354870999</v>
+        <v>23.27828304949362</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>20.46535062787453</v>
+        <v>20.53860773765422</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>22.31813453424729</v>
+        <v>22.41748185954187</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>16.7080279705819</v>
+        <v>16.80793600660057</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>19.44510882563984</v>
+        <v>19.56880544666809</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>19.02495797232639</v>
+        <v>19.17364752010422</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>19.25069362255292</v>
+        <v>19.42269238211959</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.0926</t>
+          <t>X ≈ 0.09258</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>34</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>6.342613381230358</v>
+        <v>6.313417586877726</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>7.672603758754761</v>
+        <v>7.671416972310105</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>4.33665590341149</v>
+        <v>4.336502513407169</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>19.17276339994103</v>
+        <v>19.17226890756302</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>15.6932973762571</v>
+        <v>15.74184329602287</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>15.99067140589221</v>
+        <v>16.01462881484183</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>10.02360810544958</v>
+        <v>10.0716197844399</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>12.49771593225108</v>
+        <v>12.54696349464479</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>24.2014396580812</v>
+        <v>24.2746967678609</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>23.35152086175134</v>
+        <v>23.45086818704591</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>20.20564323290287</v>
+        <v>20.30555126892155</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>17.29884491466996</v>
+        <v>17.42254153569821</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>22.76104700253306</v>
+        <v>22.90973655031089</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>20.04560618217136</v>
+        <v>20.21760494173802</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.09993</t>
+          <t>X ≈ 0.09992</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>30</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-2.480916030534353</v>
+        <v>-2.510111824886984</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.7587687902648241</v>
+        <v>-0.7599555767094799</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>5.51312649164678</v>
+        <v>5.512973101642459</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>8.976684968568492</v>
+        <v>8.976190476190489</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>8.438395415472776</v>
+        <v>8.486941335238548</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>12.06910277844119</v>
+        <v>12.0930601873908</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>8.651059085841695</v>
+        <v>8.699070764832015</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>8.183990442054956</v>
+        <v>8.233238004448673</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>11.45634161886551</v>
+        <v>11.5295987286452</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>10.60642282253565</v>
+        <v>10.70577014783022</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>17.06838833094213</v>
+        <v>17.1682963669608</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>13.76943314996412</v>
+        <v>13.89312977099237</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>16.68261562998404</v>
+        <v>16.83130517776187</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>23.57501794687725</v>
+        <v>23.74701670644391</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>16</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>3.769083969465647</v>
+        <v>3.739888175113016</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>8.407897876401776</v>
+        <v>8.40671108995712</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1.76312649164678</v>
+        <v>1.762973101642459</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-4.356648364764901</v>
+        <v>-4.357142857142904</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1.355062082139447</v>
+        <v>1.403608001905219</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.652436111774534</v>
+        <v>1.676393520724147</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>7.817725752508323</v>
+        <v>7.865737431498644</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>13.60065710872163</v>
+        <v>13.64990467111534</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>13.53967495219885</v>
+        <v>13.61293206197855</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>12.68975615586899</v>
+        <v>12.78910348116356</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>12.4850549976088</v>
+        <v>12.58496303362747</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>18.76943314996416</v>
+        <v>18.89312977099241</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>18.34928229665071</v>
+        <v>18.49797184442854</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>18.57501794687729</v>
+        <v>18.74701670644395</v>
       </c>
     </row>
   </sheetData>
@@ -2210,1249 +2210,1249 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.1017</t>
+          <t>X &gt; -0.1014</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4089</v>
+        <v>4100</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.2868643484280611</v>
+        <v>-0.2854582873231593</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.1052696437152321</v>
+        <v>-0.1049620617938132</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.2673613132312624</v>
+        <v>-0.2666425636457959</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.2214934489317315</v>
+        <v>-0.2208898157803389</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1365191770113583</v>
+        <v>-0.1372170163473925</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.02777172319752452</v>
+        <v>0.02717248859173083</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.005225752508366099</v>
+        <v>0.004159637488463375</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.05776779970327794</v>
+        <v>-0.05869250375071289</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.0412626415002677</v>
+        <v>0.03954594748402229</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.06219840069099547</v>
+        <v>-0.06421035899237637</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.008835520475258818</v>
+        <v>-0.01100333244613694</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.03403788401290342</v>
+        <v>-0.03666057518023536</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.04925071068424813</v>
+        <v>-0.05238172787089468</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.02977540112959787</v>
+        <v>-0.03347109843413421</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.09441</t>
+          <t>X &gt; -0.0941</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4068</v>
+        <v>4078</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.2633223035066621</v>
+        <v>-0.2734948608195253</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.04798447653936222</v>
+        <v>-0.05905908119198244</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.2333800050435855</v>
+        <v>-0.2439356780102671</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.212460037153285</v>
+        <v>-0.2230919765166348</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.09974537432363206</v>
+        <v>-0.1118678972873468</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.08840274572938966</v>
+        <v>0.07641799453716658</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.01711225557584584</v>
+        <v>0.004660320115576155</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.06834141852431941</v>
+        <v>-0.08050669029503155</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.08061529101544807</v>
+        <v>0.06743855230428863</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.04354443352197279</v>
+        <v>-0.05692787601429217</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.03571822531697677</v>
+        <v>0.04667584911387479</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.03478941532038959</v>
+        <v>0.04509055530609629</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.02746874783196063</v>
+        <v>-0.01759569663543914</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.03363495381104542</v>
+        <v>-0.02443988992686741</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.08708</t>
+          <t>X &gt; -0.08678</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4042</v>
+        <v>4053</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.3477471032840427</v>
+        <v>-0.3458225971447249</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.09604884288776816</v>
+        <v>-0.09574893464308332</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.255440002308319</v>
+        <v>-0.2547434337906083</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.16118933218835</v>
+        <v>-0.1607362610316159</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.01959849549570691</v>
+        <v>-0.02118274157090383</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.1184854944905851</v>
+        <v>0.1173563377642779</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.09668351985833112</v>
+        <v>0.09480147090755509</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.01100297032975561</v>
+        <v>-0.01263536337591376</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.114607000629789</v>
+        <v>0.1118231413279887</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.04455101498911063</v>
+        <v>0.04107538158260127</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.1009388047781457</v>
+        <v>0.09729044980105073</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.1245271163340504</v>
+        <v>0.1200101655669599</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.06459270971031827</v>
+        <v>0.05939266337279037</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.007477125501686999</v>
+        <v>0.001642909256638347</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.07974</t>
+          <t>X &gt; -0.07946</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4014</v>
+        <v>4023</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.3080826558137133</v>
+        <v>-0.3049582074439741</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.1179342150040412</v>
+        <v>-0.1155937427565945</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.1763145021420414</v>
+        <v>-0.1736902597854026</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.1319962772897156</v>
+        <v>-0.129520739612488</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.01052330190231032</v>
+        <v>0.01471911301633355</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.1761805175428108</v>
+        <v>0.1770757335745543</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.1548309502203793</v>
+        <v>0.1796332131364125</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.07453770573655305</v>
+        <v>0.07488605607438359</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.1765871194046227</v>
+        <v>0.1757423896846007</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.08709313944290642</v>
+        <v>0.08578835824327768</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.1204172082137234</v>
+        <v>0.1191160390919492</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.09413434518324948</v>
+        <v>0.09188753496752611</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.06161106377400216</v>
+        <v>0.05860802733111825</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.05234729416174844</v>
+        <v>0.04828441710758824</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.07241</t>
+          <t>X &gt; -0.07214</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3967</v>
+        <v>3978</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.2949863822931533</v>
+        <v>-0.2926224738471461</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.04210245041538485</v>
+        <v>0.04204943582182352</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.1128161931194356</v>
+        <v>-0.1124969409747436</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.04435266448826525</v>
+        <v>-0.04420404069350781</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.009488641495579486</v>
+        <v>0.00688113960273995</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.1948889419632138</v>
+        <v>0.1930769125956999</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.2497841319748986</v>
+        <v>0.24654044279103</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.07341069543192447</v>
+        <v>0.07058740203903824</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.1773889501847492</v>
+        <v>0.1729998500779715</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.1220779891603527</v>
+        <v>0.1164515474619066</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.2086066348883975</v>
+        <v>0.2027098309145856</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.2068229206872232</v>
+        <v>0.1996624343089408</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.1789193934248985</v>
+        <v>0.1705026310583477</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.1921089476334856</v>
+        <v>0.182411377132695</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.06507</t>
+          <t>X &gt; -0.06482</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3920</v>
+        <v>3930</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.3578547541549923</v>
+        <v>-0.3670735291730551</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.0229261317365328</v>
+        <v>-0.03443553612097361</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.1495547599431504</v>
+        <v>-0.1353395093699703</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.2090656675638414</v>
+        <v>-0.2200870195794096</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.09727948059916258</v>
+        <v>-0.1116877584400484</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.1631285761329835</v>
+        <v>0.1749968726794506</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.1942218054750029</v>
+        <v>0.2044471089180391</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.004156951390442032</v>
+        <v>0.006611988188510054</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.1017768630268776</v>
+        <v>0.08529546731526239</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.05596410693933507</v>
+        <v>0.03808670434607109</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.1204743195562941</v>
+        <v>0.1024433285677304</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.1437319770931467</v>
+        <v>0.1494878584796453</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.1460178233020812</v>
+        <v>0.1502231799665665</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.1821608040200999</v>
+        <v>0.1846757395227883</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.05774</t>
+          <t>X &gt; -0.0575</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3862</v>
+        <v>3870</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.4551095789214514</v>
+        <v>-0.4112192160793597</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.06525648601428458</v>
+        <v>-0.07474176939368249</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.3169793694428193</v>
+        <v>-0.2999617089733633</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.3535491912111439</v>
+        <v>-0.3365243004418303</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.2320601085089677</v>
+        <v>-0.2446905286438863</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.07943869575386486</v>
+        <v>0.06796133918727065</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.03470688458383364</v>
+        <v>0.02139902551467543</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.1338309988274986</v>
+        <v>-0.09493537016432896</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.05215232483914889</v>
+        <v>0.08873851359145135</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.1218565180003992</v>
+        <v>0.1568112767237082</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.112804027363012</v>
+        <v>0.1478987423803844</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.1358927772933143</v>
+        <v>0.1689562172733616</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.2480656256696108</v>
+        <v>0.2791653344827907</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.3331743425271654</v>
+        <v>0.3620037865472696</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.05041</t>
+          <t>X &gt; -0.05018</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3789</v>
+        <v>3797</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.5082700547321437</v>
+        <v>-0.5153611687190107</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.02523541915373073</v>
+        <v>0.01540103482457766</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.1973998241426997</v>
+        <v>-0.2065647134835942</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.2634659483394799</v>
+        <v>-0.2462944200532888</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.1819310721522882</v>
+        <v>-0.1695659339854814</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.001830414430358474</v>
+        <v>0.01246447998826739</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.08590278095937265</v>
+        <v>0.09759863023685966</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.002172260236775969</v>
+        <v>0.01428805265623367</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.2193006770275332</v>
+        <v>0.2285291161605585</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.2803836275273142</v>
+        <v>0.2874591770330781</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.2751393857944535</v>
+        <v>0.2823314546801114</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.2980535667406983</v>
+        <v>0.3027112397999474</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.3677519536428022</v>
+        <v>0.3700097591204852</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.5029672738764503</v>
+        <v>0.5023498642000348</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.04307</t>
+          <t>X &gt; -0.04286</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3707</v>
+        <v>3715</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.6529590412870405</v>
+        <v>-0.6185100003632371</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.1259821988872361</v>
+        <v>-0.09436244734826005</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.2641731318066931</v>
+        <v>-0.2319933413105559</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.3345875630430442</v>
+        <v>-0.3560687432867908</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.2932156358368729</v>
+        <v>-0.2936119819787493</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.06189767019046855</v>
+        <v>-0.08677144434839335</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.08347696414003281</v>
+        <v>0.05533700150675003</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.008211646830972086</v>
+        <v>-0.01945016759433571</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.2045456418540255</v>
+        <v>0.1734994187949042</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.3935421973672391</v>
+        <v>0.3597059556121991</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.3657827604120314</v>
+        <v>0.3438387732724451</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.3615064850948855</v>
+        <v>0.3364980787674554</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.4420546806852315</v>
+        <v>0.3870999391540551</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.5483117154232389</v>
+        <v>0.4899507575879198</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.03574</t>
+          <t>X &gt; -0.03554</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3585</v>
+        <v>3593</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.5631839571602484</v>
+        <v>-0.5822338775915625</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.07486553755425263</v>
+        <v>-0.09772842169655149</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.5102327964511062</v>
+        <v>-0.5042347806778267</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.4484425233184055</v>
+        <v>-0.4981756167208786</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.5265461538093561</v>
+        <v>-0.5559171300025838</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.2418722656259646</v>
+        <v>-0.2958287014980741</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.0783048170963454</v>
+        <v>0.01980800665845095</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.03934567601799444</v>
+        <v>-0.0695227885844858</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.05429890763060996</v>
+        <v>0.02000740254012356</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.2785691957129615</v>
+        <v>0.240438297626298</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.3404061681773598</v>
+        <v>0.3143846131602928</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.4463219149487898</v>
+        <v>0.4438947223136438</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.488155693192823</v>
+        <v>0.481833836637783</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.5066776400432147</v>
+        <v>0.4962513293217299</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.0284</t>
+          <t>X &gt; -0.02822</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3437</v>
+        <v>3444</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.4809160305343525</v>
+        <v>-0.4255721607294802</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.1344332340649856</v>
+        <v>-0.1112443111433308</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.3685440419959107</v>
+        <v>-0.3155321127260251</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.5127261135319046</v>
+        <v>-0.4886989278469969</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.5130458691083746</v>
+        <v>-0.4695804038918823</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.2579412467160296</v>
+        <v>-0.2390167431204517</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.1526575227529605</v>
+        <v>-0.1679052599166226</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.08108846200157416</v>
+        <v>-0.1247544527604916</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.01919267445335748</v>
+        <v>-0.02969707325070914</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.2896544412511517</v>
+        <v>0.249202146282542</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.1885433697018186</v>
+        <v>0.161138309309429</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.501041175552956</v>
+        <v>0.4804774204410052</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.5627785153825329</v>
+        <v>0.5371590722950117</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.4851139608429165</v>
+        <v>0.4543337796146361</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.02107</t>
+          <t>X &gt; -0.0209</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3249</v>
+        <v>3255</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.4723297073206183</v>
+        <v>-0.4868132350647869</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.1963966021257875</v>
+        <v>-0.2141107438361516</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.482577712096699</v>
+        <v>-0.4992968370078472</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.5813260811552894</v>
+        <v>-0.6290053916626519</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.4276367204396152</v>
+        <v>-0.4265024953323504</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.3592346498962229</v>
+        <v>-0.3685727162310428</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.2289572941746769</v>
+        <v>-0.2283675731067802</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.09557945041815685</v>
+        <v>-0.1108414142392817</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.07547704193456184</v>
+        <v>0.06710768371634401</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.3184834844887305</v>
+        <v>0.3178876383634446</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.1618692657514771</v>
+        <v>0.1751533928537583</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.4289225378447767</v>
+        <v>0.4482418373110661</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.4569746043430172</v>
+        <v>0.469716316173006</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.3309428468464688</v>
+        <v>0.3368784575959793</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.01374</t>
+          <t>X &gt; -0.01357</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2981</v>
+        <v>2983</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.6748959636447154</v>
+        <v>-0.6198475224446938</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.2459482774443345</v>
+        <v>-0.3114950680080284</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.85689692755696</v>
+        <v>-0.8880982073632353</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.6932157786156381</v>
+        <v>-0.7402640895608101</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.4438000329877312</v>
+        <v>-0.4410318640914284</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.4141636204878552</v>
+        <v>-0.4362530454400115</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.1307347561931067</v>
+        <v>-0.1436459465174025</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.1235061211086403</v>
+        <v>0.09427464430569188</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.1815034853535735</v>
+        <v>0.1578382281983863</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.4891698912123701</v>
+        <v>0.439907770707805</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.4374678662415121</v>
+        <v>0.369815580544369</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.7590409273694192</v>
+        <v>0.6625667683114003</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.7604157641222145</v>
+        <v>0.7030656782087021</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.4351320025632504</v>
+        <v>0.3678681982307026</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.006402</t>
+          <t>X &gt; -0.006254</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2643</v>
+        <v>2641</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.6891393424921048</v>
+        <v>-0.6400702684079533</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.0006930480351670099</v>
+        <v>0.06392953288989389</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.24159048948529</v>
+        <v>-1.178898353934102</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.149101194953538</v>
+        <v>-1.18013831856495</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.045881314086969</v>
+        <v>-1.006059043119372</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.7862431335084779</v>
+        <v>-0.7711093169602989</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.4935950022086146</v>
+        <v>-0.4707500779638423</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.1097052921843797</v>
+        <v>-0.1795805673403734</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.03660903571655183</v>
+        <v>-0.02730260872546353</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.5321248751738636</v>
+        <v>0.5493230118221533</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.6511547708514343</v>
+        <v>0.6858335862391272</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.047315947695694</v>
+        <v>1.008951118456416</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.102686230084899</v>
+        <v>1.105844668047006</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.8584080338995719</v>
+        <v>0.9223290881175146</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 0.0009315</t>
+          <t>X &gt; 0.001067</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2208</v>
+        <v>2206</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.809732652033901</v>
+        <v>-0.7001570737557543</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.01810564514617852</v>
+        <v>0.1846649152174606</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.099339633014466</v>
+        <v>-0.9997080577778306</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.420785672804605</v>
+        <v>-1.344002848080784</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.236401332494694</v>
+        <v>-1.129256911966039</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.164862894548861</v>
+        <v>-1.128456887254096</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.662400715422983</v>
+        <v>-0.5998110725810903</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.3164612291284143</v>
+        <v>-0.2950182663279932</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.4430408182484982</v>
+        <v>-0.377321791149285</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.4044939497207096</v>
+        <v>0.4760935083621192</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.5419297149312712</v>
+        <v>0.6346003863019973</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.7830078105976028</v>
+        <v>0.8740907864048779</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.067706923178555</v>
+        <v>1.158896595108509</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.8213947584714489</v>
+        <v>0.9093013845944071</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.008265</t>
+          <t>X &gt; 0.008387</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1794</v>
+        <v>1792</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.3142493638676882</v>
+        <v>-0.3095547218229129</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.2412312097351546</v>
+        <v>0.1987958168245001</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.04242906390877</v>
+        <v>-1.0570213211127</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.13442614254263</v>
+        <v>-1.120535714285722</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.117160140082774</v>
+        <v>-1.107552712380489</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.20867499933658</v>
+        <v>-1.225392193561561</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.071163136380527</v>
+        <v>-1.062833997072744</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.4826762246117084</v>
+        <v>-0.5242024717417948</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.06857963368219089</v>
+        <v>-0.003139366592883164</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.6138384695508634</v>
+        <v>0.6239249097349955</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.6632686870912607</v>
+        <v>0.6988023193417661</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.508854085376143</v>
+        <v>1.370808342420936</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.510842185230096</v>
+        <v>1.477882558714249</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.434549719452491</v>
+        <v>1.336302420729616</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.0156</t>
+          <t>X &gt; 0.01571</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.1192426162293643</v>
+        <v>-0.01011182488698381</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.901150238075239</v>
+        <v>1.011511630863183</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.4382905124017995</v>
+        <v>-0.2921689822546938</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.5104945186110115</v>
+        <v>-0.4641164522681152</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.723547904365276</v>
+        <v>-1.630413663633036</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.763555791059467</v>
+        <v>-1.696152180020611</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.915742533591498</v>
+        <v>-1.824513076287374</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.100759895326952</v>
+        <v>-1.003954502886003</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.8551596190367974</v>
+        <v>-0.8378126908989074</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.02083723695007933</v>
+        <v>0.03097890431860861</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.3949603390557215</v>
+        <v>0.3684769131129144</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.279581999761149</v>
+        <v>1.239101334973412</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.101482702879551</v>
+        <v>0.9793530224921838</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.8243404401021763</v>
+        <v>0.6867594281771545</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.02293</t>
+          <t>X &gt; 0.02303</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.4947755034136776</v>
+        <v>0.6724677396021264</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.48208060900869</v>
+        <v>1.6485384160259</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.1700252267103011</v>
+        <v>-0.04071817352532747</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.2912669733147268</v>
+        <v>-0.2009715725081023</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.248668010065082</v>
+        <v>-1.110035994736258</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.454227760815577</v>
+        <v>-1.341028813448808</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.203648933158014</v>
+        <v>-1.06583267765329</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.581027719442659</v>
+        <v>-0.440145706718404</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.4743652825035767</v>
+        <v>-0.3091922033447077</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.5672729343924843</v>
+        <v>0.7141664534557535</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.417674644963959</v>
+        <v>1.517582680982635</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1.871868078595519</v>
+        <v>1.91160164336852</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.70360639404786</v>
+        <v>1.768332885570437</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1.810312064524311</v>
+        <v>1.849451635075305</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.03027</t>
+          <t>X &gt; 0.03035</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.341073498261458</v>
+        <v>1.36018106214231</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.82412824289397</v>
+        <v>1.927653498334124</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.115220732484474</v>
+        <v>1.173350460133022</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.5124615828791192</v>
+        <v>0.4646600778676131</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.3399640958710251</v>
+        <v>-0.2342326689543199</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.3567261918903881</v>
+        <v>-0.2759125589404192</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.5009718258068006</v>
+        <v>0.6068275782492165</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.5574633914441378</v>
+        <v>0.6651038325409147</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.391769193036545</v>
+        <v>0.5233094204691113</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1.486925967189748</v>
+        <v>1.586273292484321</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>2.496859824471336</v>
+        <v>2.535172677233348</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3.265760537162443</v>
+        <v>3.327092035143309</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>2.635746095181666</v>
+        <v>2.72229050270947</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3.071345334075566</v>
+        <v>3.18097897059485</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.0376</t>
+          <t>X &gt; 0.03767</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.429136879518552</v>
+        <v>0.4621470918897685</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.860278828782775</v>
+        <v>1.859092042338119</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.523708502228793</v>
+        <v>2.523555112224471</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>2.653933645817155</v>
+        <v>2.653439153439152</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.9251679022452706</v>
+        <v>0.9737138220110424</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.413018122356547</v>
+        <v>2.43697553130616</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>3.25423368901631</v>
+        <v>3.302245368006631</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.654889912954431</v>
+        <v>2.704137475348148</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.25528341780732</v>
+        <v>3.328540527587016</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3.409954831365681</v>
+        <v>3.430637872697957</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>4.927107977741251</v>
+        <v>4.946074144738589</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>5.888638447977371</v>
+        <v>5.930166808029405</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>5.600937925789779</v>
+        <v>5.667284013740712</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>5.429322582638839</v>
+        <v>5.519503478930673</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.04494</t>
+          <t>X &gt; 0.04499</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>616</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.090512540894217</v>
+        <v>1.061316746541586</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>2.726079694583639</v>
+        <v>2.724892908138983</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3.792347270867552</v>
+        <v>3.792193880863231</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>4.734260726144235</v>
+        <v>4.733766233766232</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>2.897269874347245</v>
+        <v>2.945815794113017</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>3.519319228657658</v>
+        <v>3.543276637607271</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>4.246297181079797</v>
+        <v>4.294308860070117</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>3.779228537293058</v>
+        <v>3.828476099686775</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>3.880584043107945</v>
+        <v>3.953841152887641</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>4.816379532492363</v>
+        <v>4.915726857786936</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>6.559730322284125</v>
+        <v>6.6596383583028</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>7.568134448665418</v>
+        <v>7.691831069693663</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>7.147983595352009</v>
+        <v>7.296673143129837</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>7.049043920903216</v>
+        <v>7.221042680469878</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.05227</t>
+          <t>X &gt; 0.05231</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>493</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2.285818249384505</v>
+        <v>2.256622455031874</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>3.717228505205064</v>
+        <v>3.716041718760408</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>4.94517517318836</v>
+        <v>4.945021783184039</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5.6839195865536</v>
+        <v>5.683425094175597</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>4.131431250496441</v>
+        <v>4.179977170262212</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>5.037324549908405</v>
+        <v>5.061281958858018</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>4.952614190642237</v>
+        <v>5.000625869632557</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>4.079866033670925</v>
+        <v>4.129113596064641</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>4.424563390332722</v>
+        <v>4.497820500112418</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>5.603042159925785</v>
+        <v>5.702389485220358</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>7.223898810996218</v>
+        <v>7.323806847014893</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>7.258276963351541</v>
+        <v>7.381973584379786</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>7.04096586663043</v>
+        <v>7.189655414408257</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>7.672381030041556</v>
+        <v>7.844379789608219</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.0596</t>
+          <t>X &gt; 0.05963</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3.24047700429152</v>
+        <v>3.489888175113023</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>5.609390413715246</v>
+        <v>5.906711089957163</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>5.712131466771162</v>
+        <v>5.762973101642459</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>6.339869048170463</v>
+        <v>6.642857142857139</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>4.060285962736465</v>
+        <v>4.403608001905219</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>5.601441086898916</v>
+        <v>5.926393520724147</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>6.262999384349158</v>
+        <v>6.365737431498687</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>5.298418302751472</v>
+        <v>5.399904671115344</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>5.734948584039643</v>
+        <v>5.862932061978547</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>5.880054663331677</v>
+        <v>6.039103481163565</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>7.914159475220742</v>
+        <v>8.084963033627474</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>7.948537627576066</v>
+        <v>8.393129770992367</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>7.528386774262657</v>
+        <v>7.997971844428541</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>8.251634862300143</v>
+        <v>8.747016706443908</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.06694</t>
+          <t>X &gt; 0.06695</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>328</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>4.836157140197351</v>
+        <v>4.806961345844719</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>7.493263730060356</v>
+        <v>7.4920769436157</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>7.098492345305317</v>
+        <v>7.098338955300996</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>9.057985781576605</v>
+        <v>9.057491289198602</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>6.995305984578472</v>
+        <v>7.043851904344244</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>7.902436111774534</v>
+        <v>7.926393520724147</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>9.646994045191292</v>
+        <v>9.695005724181613</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>8.26529125506309</v>
+        <v>8.314538817456807</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>8.204309098540314</v>
+        <v>8.27756620832001</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>8.269024448551917</v>
+        <v>8.368371773846491</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>10.80822572931612</v>
+        <v>10.9081337653348</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>11.14748193045192</v>
+        <v>11.27117855148017</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>10.42245302835803</v>
+        <v>10.57114257613586</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>10.34331062980407</v>
+        <v>10.51530938937074</v>
       </c>
     </row>
     <row r="30">
@@ -3465,202 +3465,202 @@
         <v>266</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>5.789760661194975</v>
+        <v>5.760564866842344</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>6.810153515499564</v>
+        <v>6.808966729054909</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>7.919141529240768</v>
+        <v>7.918988139236447</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>9.929065920949434</v>
+        <v>9.928571428571431</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>7.511077119733436</v>
+        <v>7.559623039499208</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>9.688150397488826</v>
+        <v>9.712107806438439</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>10.35531973747077</v>
+        <v>10.40333141646109</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>9.888251093684026</v>
+        <v>9.937498656077743</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>10.95508848603343</v>
+        <v>11.02834559581313</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>11.60892908819982</v>
+        <v>11.70827641349439</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>11.40422792993962</v>
+        <v>11.5041359659583</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>11.81454593191901</v>
+        <v>11.93824255294725</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>12.14627477785372</v>
+        <v>12.29496432563155</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>12.74795027770431</v>
+        <v>12.91994903727097</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.08161</t>
+          <t>X &gt; 0.08159</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>201</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.245452128669619</v>
+        <v>2.216256334316988</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>6.1069028515262</v>
+        <v>6.105716065081545</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>8.697206093636829</v>
+        <v>8.697052703632508</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>10.81748098846898</v>
+        <v>10.81698649609098</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>8.786654121940444</v>
+        <v>8.835200041706216</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>11.57159034063025</v>
+        <v>11.59554774957986</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>11.98439241917502</v>
+        <v>12.03240409816534</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>11.51732377538828</v>
+        <v>11.566571337782</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>13.4463913701093</v>
+        <v>13.51964847988899</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>13.09398501159038</v>
+        <v>13.19333233688495</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>13.88430872895209</v>
+        <v>13.98421676497077</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>14.41619931911836</v>
+        <v>14.5398959401466</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>15.98609821704872</v>
+        <v>16.13478776482655</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>16.21183386727525</v>
+        <v>16.38383262684192</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.08894</t>
+          <t>X &gt; 0.08892</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>164</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-1.871159932973377</v>
+        <v>-1.900355727326009</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>3.224971047133522</v>
+        <v>3.223784260688866</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>6.488736247744342</v>
+        <v>6.48858285774002</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>7.838473586454654</v>
+        <v>7.837979094076651</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>7.30018403335896</v>
+        <v>7.348729953124732</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>10.03658245323795</v>
+        <v>10.06053986218757</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>9.342115996410811</v>
+        <v>9.390127675401132</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>8.875047352624073</v>
+        <v>8.924294915017789</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>11.86284568390617</v>
+        <v>11.93610279368587</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>11.01292688757631</v>
+        <v>11.11227421287089</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>13.24725011956001</v>
+        <v>13.34715815557868</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>13.28162827191533</v>
+        <v>13.40532489294358</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>15.30050180884584</v>
+        <v>15.44919135662366</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>15.52623745907237</v>
+        <v>15.69823621863903</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.09627</t>
+          <t>X &gt; 0.09624</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>130</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-4.019377568995893</v>
+        <v>-4.048573363348524</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>2.061744030247972</v>
+        <v>2.060557243803316</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>7.05158803010832</v>
+        <v>7.051434640103999</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>4.874120866004375</v>
+        <v>4.873626373626372</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>5.105062082139447</v>
+        <v>5.153608001905219</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>8.479359188697607</v>
+        <v>8.50331659764722</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>9.163879598662206</v>
+        <v>9.211891277652526</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>7.9275801856447</v>
+        <v>7.976827748038417</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>8.635828798352691</v>
+        <v>8.709085908132387</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>7.785910002022831</v>
+        <v>7.885257327317404</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>11.42736268991649</v>
+        <v>11.52727072593517</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>12.23097161150259</v>
+        <v>12.35466823253083</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>13.34928229665071</v>
+        <v>13.49797184442854</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>14.34424871610802</v>
+        <v>14.51624747567468</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>100</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-4.480916030534353</v>
+        <v>-4.510111824886984</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>2.907897876401812</v>
+        <v>2.906711089957156</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>7.51312649164678</v>
+        <v>7.512973101642459</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3.643351635235135</v>
+        <v>3.642857142857132</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>4.105062082139447</v>
+        <v>4.153608001905219</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>7.402436111774534</v>
+        <v>7.426393520724147</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>9.317725752508366</v>
+        <v>9.365737431498687</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>7.850657108721627</v>
+        <v>7.899904671115344</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>7.789674952198851</v>
+        <v>7.862932061978547</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>6.939756155868992</v>
+        <v>7.039103481163565</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>9.735054997608799</v>
+        <v>9.834963033627474</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>11.76943314996412</v>
+        <v>11.89312977099237</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>12.34928229665071</v>
+        <v>12.49797184442854</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>11.57501794687725</v>
+        <v>11.74701670644391</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-6.052344601962922</v>
+        <v>-6.081540396315553</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>1.860278828782775</v>
+        <v>1.859092042338119</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>8.608364586884875</v>
+        <v>8.608211196880553</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>5.167161159044667</v>
+        <v>5.166666666666664</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>4.628871605948973</v>
+        <v>4.677417525714745</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>8.497674207012629</v>
+        <v>8.521631615962242</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>9.603440038222658</v>
+        <v>9.651451717212979</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>6.755419013483532</v>
+        <v>6.804666575877249</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>6.694436856960756</v>
+        <v>6.767693966740453</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>5.844518060630897</v>
+        <v>5.94386538592547</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>9.211245473799281</v>
+        <v>9.311153509817956</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>10.43609981663078</v>
+        <v>10.55979643765902</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>11.20642515379357</v>
+        <v>11.3551147015714</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>10.2416846135439</v>
+        <v>10.41368337311057</v>
       </c>
     </row>
   </sheetData>
@@ -3904,1249 +3904,1249 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.1017</t>
+          <t>X &lt; -0.1014</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>12.99527444565613</v>
+        <v>12.9660786513035</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>6.622183590687527</v>
+        <v>6.620996804242871</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>12.17979315831344</v>
+        <v>12.17963976830912</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>11.11954211142562</v>
+        <v>11.11904761904762</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>7.009823986901353</v>
+        <v>7.058369906667124</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1643408736793006</v>
+        <v>0.1882982826289137</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>2.460582895365505</v>
+        <v>2.508594574355826</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>5.564942823007335</v>
+        <v>5.614190385401052</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>1.93253209505599</v>
+        <v>2.005789204835686</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>7.034994251107086</v>
+        <v>7.13434157640166</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>4.449340711894507</v>
+        <v>4.549248747913182</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>5.674195054726027</v>
+        <v>5.797891675754272</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>6.444520391888808</v>
+        <v>6.593209939666636</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>5.479779851639151</v>
+        <v>5.651778611205813</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.09441</t>
+          <t>X &lt; -0.0941</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>9.423845874227553</v>
+        <v>9.75403911850924</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3.050755019258958</v>
+        <v>3.45388090127792</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>8.370269348789634</v>
+        <v>8.720520271453779</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>8.500494492377996</v>
+        <v>8.850404312668459</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>4.152681129758498</v>
+        <v>4.587570266056161</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-2.216611507273079</v>
+        <v>-1.743417800030571</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1.508201942984556</v>
+        <v>1.969511016404347</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>4.850657108721627</v>
+        <v>5.277263161681383</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.02777019029409189</v>
+        <v>0.5233094204691113</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>4.892137108249948</v>
+        <v>5.359858198144693</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>1.830293092846901</v>
+        <v>1.382132844948231</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>1.864671245202224</v>
+        <v>1.440299582313123</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>4.30166324903167</v>
+        <v>3.87533033499458</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>4.527398899258202</v>
+        <v>4.124375197009947</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.08708</t>
+          <t>X &lt; -0.08678</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>131</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>10.1145038167939</v>
+        <v>10.08530802244127</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>3.923165051974337</v>
+        <v>3.921978265529681</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>7.345187560349075</v>
+        <v>7.345034170344753</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>5.185336368059566</v>
+        <v>5.184841875681563</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.8302529218341093</v>
+        <v>0.8787988415998811</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-2.689166941660581</v>
+        <v>-2.665209532710968</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-1.247159743674843</v>
+        <v>-1.199148064684522</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>2.102565505668188</v>
+        <v>2.151813068061905</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-1.011851765358401</v>
+        <v>-0.9385946555787044</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>1.191664552815553</v>
+        <v>1.291011878110126</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.5397541626965392</v>
+        <v>-0.4398461266778639</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-1.268734788967173</v>
+        <v>-1.145038167938928</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.6011906935972746</v>
+        <v>0.7498802413751022</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>2.353643901075721</v>
+        <v>2.525642660642383</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.07974</t>
+          <t>X &lt; -0.07946</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>7.267511642421617</v>
+        <v>7.117217367659599</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>3.769533096527603</v>
+        <v>3.670686245236666</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>4.003692529382626</v>
+        <v>3.898066269344319</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>3.504986855360926</v>
+        <v>3.406832298136642</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.450974031824984</v>
+        <v>-0.1880069049270787</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-3.654167661810369</v>
+        <v>-3.641929460642316</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-2.481016385856414</v>
+        <v>-3.081467537445413</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.4323617592029052</v>
+        <v>-0.441710235716954</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-2.380136368555867</v>
+        <v>-2.34203688212083</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.08540107683541009</v>
+        <v>-0.06027540082401828</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.9190330527056645</v>
+        <v>-0.8855338607824592</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.2557240827402794</v>
+        <v>-0.2062491109952163</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.5819866991664355</v>
+        <v>0.6408289872856798</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.8077223493929679</v>
+        <v>0.889873849301047</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.07241</t>
+          <t>X &lt; -0.07214</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>206</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>5.28607426072778</v>
+        <v>5.256878466375149</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.2086069779671149</v>
+        <v>-0.2097937644117707</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1.823806103297265</v>
+        <v>1.823652713292944</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.9831574604778552</v>
+        <v>0.9826629680998522</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.04056898582172153</v>
+        <v>0.007976933944050302</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-3.141253208613819</v>
+        <v>-3.117295799664205</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-3.711400461083869</v>
+        <v>-3.663388782093548</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.2949739592395417</v>
+        <v>-0.245726396845825</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-1.812266795373965</v>
+        <v>-1.739009685594269</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.7204380188882951</v>
+        <v>-0.6210906935937217</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-2.381449856760135</v>
+        <v>-2.28154182074146</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-2.347071704404811</v>
+        <v>-2.223375083376567</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-1.796348771310456</v>
+        <v>-1.647659223532628</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-2.056050014287806</v>
+        <v>-1.884051254721143</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.06507</t>
+          <t>X &lt; -0.06482</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>5.22659385088857</v>
+        <v>5.363903923144512</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.8486093388524196</v>
+        <v>1.024821326177637</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.034865622081561</v>
+        <v>1.812185700067658</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>3.350861516658064</v>
+        <v>3.516872890888635</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.626801212574229</v>
+        <v>1.84652138773199</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-2.028393927751161</v>
+        <v>-2.211401754866408</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-2.113104287017329</v>
+        <v>-2.272057844091869</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.9771393221603617</v>
+        <v>0.8054164821389662</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.2696135853505481</v>
+        <v>-0.01895770180097855</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.4614952863037729</v>
+        <v>0.7320168669903353</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.5337197059485135</v>
+        <v>-0.2595251553489035</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.8945984705892371</v>
+        <v>-0.9887599927871591</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.9194924069065991</v>
+        <v>-0.9902171319494073</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.484270590672153</v>
+        <v>-1.528573844737188</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.05774</t>
+          <t>X &lt; -0.0575</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>5.396897474288799</v>
+        <v>4.814728939444223</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.213364114343946</v>
+        <v>1.320723828810664</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>3.712483404830053</v>
+        <v>3.474756541132905</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>4.485795365138678</v>
+        <v>4.241583257506818</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>2.982875586962599</v>
+        <v>3.115391441395666</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.5782712837238506</v>
+        <v>-0.4334790907408248</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.3016485820903512</v>
+        <v>0.461278832772571</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2.406927205184651</v>
+        <v>1.906274097866934</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.4166845985010994</v>
+        <v>-0.04152653674756834</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.4332341978287602</v>
+        <v>-0.8653551175625509</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.3163919477288246</v>
+        <v>-0.7510242275190251</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.6035572037336294</v>
+        <v>-1.011328827733749</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.988338282127422</v>
+        <v>-2.361900767036431</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-3.048776265341402</v>
+        <v>-3.38674125533953</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.05041</t>
+          <t>X &lt; -0.05018</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>4.810750636132312</v>
+        <v>4.854229260384336</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.07456454306848315</v>
+        <v>0.1702769814300282</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.76312649164678</v>
+        <v>1.843722455647629</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2.674601635235142</v>
+        <v>2.490402362495381</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.875895415472783</v>
+        <v>1.742755288726926</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.3503527784411986</v>
+        <v>0.2067552778300907</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.2551909141582982</v>
+        <v>-0.3706966770284481</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.5798237753882916</v>
+        <v>0.4554602266709011</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.304075047801149</v>
+        <v>-1.390297912181659</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.893577177464344</v>
+        <v>-1.955728560180106</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.837861669057865</v>
+        <v>-1.901471074899661</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-2.063900183369213</v>
+        <v>-2.101702270351304</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.744467703349287</v>
+        <v>-2.755258129731665</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-4.081232053122754</v>
+        <v>-4.056600864615525</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.04307</t>
+          <t>X &lt; -0.04286</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>5.029813583199548</v>
+        <v>4.723930728304502</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.272704743354609</v>
+        <v>1.013094068680566</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.950894731990125</v>
+        <v>1.68318586759991</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.72489669961282</v>
+        <v>2.876899696048625</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2.401199421195244</v>
+        <v>2.387650555096705</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.7672429787273245</v>
+        <v>0.9583084143411682</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.1758364792512879</v>
+        <v>0.04658849532847142</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.4300562503525285</v>
+        <v>0.6445855221791774</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.918479554238921</v>
+        <v>-0.6689828316384734</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.412175174603114</v>
+        <v>-2.13110928479388</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.187691783507077</v>
+        <v>-2.007254450381055</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-2.153313631151754</v>
+        <v>-1.949087713016162</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-2.788056759143281</v>
+        <v>-2.344245639579988</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-3.635282482307304</v>
+        <v>-3.161298858588083</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.03574</t>
+          <t>X &lt; -0.03554</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>3.301396894635708</v>
+        <v>3.402050337275178</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.6698026383065852</v>
+        <v>0.8053597386058158</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.996119688925688</v>
+        <v>2.945405534074894</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.786208778092281</v>
+        <v>3.075289575289574</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>3.268327388261895</v>
+        <v>3.430635028932251</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.69495311857726</v>
+        <v>2.014231358561986</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.09043751279775591</v>
+        <v>0.2643860801473394</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.6329700338916879</v>
+        <v>0.8120668332775054</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.2318518229471422</v>
+        <v>0.4372563863028702</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.128271055015361</v>
+        <v>-0.8933289512688702</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.503040240486435</v>
+        <v>-1.342701940991816</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.14893419697465</v>
+        <v>-2.130558892290203</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.399017023077178</v>
+        <v>-2.356512081121373</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.513417427272415</v>
+        <v>-2.445876694571325</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.0284</t>
+          <t>X &lt; -0.02822</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2.138649186856959</v>
+        <v>1.864046990725399</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.7992022242279049</v>
+        <v>0.684638411626068</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.627256926429382</v>
+        <v>1.367616439462111</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2.436829896104712</v>
+        <v>2.305037492789836</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>2.44201860387858</v>
+        <v>2.219556857894453</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.380696981339753</v>
+        <v>1.2810368585438</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.024247491638796</v>
+        <v>1.085791267299498</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.6930484130694552</v>
+        <v>0.8891375109538302</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.3603271261118977</v>
+        <v>0.5829858977793592</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.8972003658701411</v>
+        <v>-0.7048318288094819</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.4225536980433731</v>
+        <v>-0.2945916222429688</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.882740763079362</v>
+        <v>-1.78254590468331</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.167022051175373</v>
+        <v>-2.042568696111999</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.805416835731442</v>
+        <v>-1.658388698961502</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.02107</t>
+          <t>X &lt; -0.0209</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>924</v>
+        <v>929</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.573138023519704</v>
+        <v>1.607535233936545</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.8268167953207453</v>
+        <v>0.8799731220427205</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.621234599754892</v>
+        <v>1.66270572196332</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.075784067667577</v>
+        <v>2.220397249809011</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.537494514571883</v>
+        <v>1.517244365541579</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.402436111774541</v>
+        <v>1.422110865477897</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.053656488439103</v>
+        <v>1.040255632783484</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.5865878446523638</v>
+        <v>0.6340954535376326</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.09270525522914852</v>
+        <v>0.1204427915922821</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.757213541100711</v>
+        <v>-0.7514443169030258</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.2043389417851458</v>
+        <v>-0.2510584717488769</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.143986763455793</v>
+        <v>-1.209130724163707</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.239462292093876</v>
+        <v>-1.281360771287289</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.797276425417131</v>
+        <v>-0.8170306563117435</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.01374</t>
+          <t>X &lt; -0.01357</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1192</v>
+        <v>1201</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.616073936020832</v>
+        <v>1.463398108887851</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.7196133575733725</v>
+        <v>0.8735985071757071</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2.082164148550547</v>
+        <v>2.135489657933853</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.757254482806324</v>
+        <v>1.851466414380319</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.135212835908298</v>
+        <v>1.113872902567465</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.144263437843271</v>
+        <v>1.184471399763083</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.5190680343875584</v>
+        <v>0.5438650205624853</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.1157858442985074</v>
+        <v>-0.04205221114003876</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.1767680008212835</v>
+        <v>-0.1163210500546441</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.9427941797014796</v>
+        <v>-0.8113948577068726</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.8119248681630111</v>
+        <v>-0.6371899173284703</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.61647289030433</v>
+        <v>-1.364773723184008</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.617160656369421</v>
+        <v>-1.464559379551474</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.8041766839952444</v>
+        <v>-0.632666890558589</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.006402</t>
+          <t>X &lt; -0.006254</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1530</v>
+        <v>1543</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.134719148618743</v>
+        <v>1.038275271887215</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.07999696375513565</v>
+        <v>-0.02877278101058067</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2.097220363876247</v>
+        <v>1.964586004868274</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.003429913121636</v>
+        <v>2.029953917050683</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.828299680050669</v>
+        <v>1.73425316319554</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.444238855079561</v>
+        <v>1.397988097870694</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.004000262312289</v>
+        <v>0.9499853333708614</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.3408531871530016</v>
+        <v>0.4554602266709011</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.2798710306302254</v>
+        <v>0.2604756948163001</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.7007667199479997</v>
+        <v>-0.7215692225880517</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.9054678782081922</v>
+        <v>-0.9546809793175086</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.590043974218887</v>
+        <v>-1.508424633152707</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.683397441911374</v>
+        <v>-1.673771512668019</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.261583360312294</v>
+        <v>-1.359917836653956</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 0.0009315</t>
+          <t>X &lt; 0.001067</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1965</v>
+        <v>1978</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.8659399532384739</v>
+        <v>0.7359878228231409</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.04285475108472525</v>
+        <v>-0.1426094938374973</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.198405679464038</v>
+        <v>1.07412056012258</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.61084782619502</v>
+        <v>1.505967359263778</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.405875090269525</v>
+        <v>1.268353849917304</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.375999914519831</v>
+        <v>1.317632191419015</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.8619780414198672</v>
+        <v>0.7813545599621676</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.4740667779328263</v>
+        <v>0.4442595098250166</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.6675375476187</v>
+        <v>0.5865830957657394</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.2841624191946224</v>
+        <v>-0.3604928861421826</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.4379729922130764</v>
+        <v>-0.5365664969126556</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.7089383513081415</v>
+        <v>-0.8038399259773357</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.027308034138088</v>
+        <v>-1.120522344555795</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.7506817986698309</v>
+        <v>-0.8434787435055355</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.008265</t>
+          <t>X &lt; 0.008387</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2379</v>
+        <v>2392</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.2013974648554253</v>
+        <v>0.1959664432229289</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.1298379726547836</v>
+        <v>-0.09661946791127463</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.756415082250804</v>
+        <v>0.7586017444401278</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.8678585592804637</v>
+        <v>0.8468538122992726</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.8565314356239071</v>
+        <v>0.8387391972404998</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.9673248140004915</v>
+        <v>0.9680601873908117</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.9059610466260182</v>
+        <v>0.8888720709317752</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.4622586219624907</v>
+        <v>0.4878946627750551</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.1911041241198319</v>
+        <v>0.1403621829631092</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.3225389260982254</v>
+        <v>-0.326505867751294</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.3591022113025133</v>
+        <v>-0.3821559642848484</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.9972755511708087</v>
+        <v>-0.8854834286734601</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.9970817218444523</v>
+        <v>-0.9650452888769294</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.9394839446738246</v>
+        <v>-0.8600067049273292</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.0156</t>
+          <t>X &lt; 0.01571</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2697</v>
+        <v>2707</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.03387686887392505</v>
+        <v>-0.02575407737133872</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.4480029745045755</v>
+        <v>-0.5047721636313511</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.2133485493817986</v>
+        <v>0.1320382470233881</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.2897788844021179</v>
+        <v>0.2619222882380683</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.9569139339913022</v>
+        <v>0.8973487971924072</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.015626182170976</v>
+        <v>0.9696716054386982</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.13685103049206</v>
+        <v>1.076864918602595</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.6904791331932572</v>
+        <v>0.6315670374994156</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.5924187415944786</v>
+        <v>0.5782712950168971</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.1132822960247211</v>
+        <v>0.1069751152469323</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.09141886223547147</v>
+        <v>-0.07647608076367618</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.5761360009442953</v>
+        <v>-0.551314673452076</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.477191563193557</v>
+        <v>-0.4089705484813564</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.3256123831190436</v>
+        <v>-0.2500279924847888</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.02293</t>
+          <t>X &lt; 0.02303</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2983</v>
+        <v>2993</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.2256537518841668</v>
+        <v>-0.2956596104347753</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.5493213749350829</v>
+        <v>-0.6134354301893552</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.04338393063039803</v>
+        <v>-0.00817241950306169</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.1249569864057136</v>
+        <v>0.08841158841158148</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.5082069466426233</v>
+        <v>0.4500770225581121</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.6233196459110815</v>
+        <v>0.5746774260890248</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.5570963584675255</v>
+        <v>0.4990707648320196</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.3094648783130509</v>
+        <v>0.251688599091338</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.3005627243931599</v>
+        <v>0.2331788931993657</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.1138451841645107</v>
+        <v>-0.1717740630473159</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.4525496925084553</v>
+        <v>-0.4908046566261959</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.6340521047275658</v>
+        <v>-0.6477717315118028</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.5662389906439529</v>
+        <v>-0.5902045082768694</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.608689729958158</v>
+        <v>-0.6231804201848874</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.03027</t>
+          <t>X &lt; 0.03035</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3220</v>
+        <v>3230</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.4227297105095928</v>
+        <v>-0.4274212972720477</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.5007708542483442</v>
+        <v>-0.5295740072350554</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.3524665712209796</v>
+        <v>-0.3679278548524465</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.1435132966112107</v>
+        <v>-0.128747795414462</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.1097103622757984</v>
+        <v>0.07796737208119708</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.1451515488483111</v>
+        <v>0.1206492341274839</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.0776230847009387</v>
+        <v>-0.1084670788504027</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.0935116257696933</v>
+        <v>-0.1248172077474479</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.01330363917564625</v>
+        <v>-0.05206021004618577</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.3357635462718704</v>
+        <v>-0.3641123506236923</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.6335456849850658</v>
+        <v>-0.6438492150579549</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.8612310337726896</v>
+        <v>-0.8779098329680295</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.6743128601329005</v>
+        <v>-0.6988712382084117</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.8038640407003967</v>
+        <v>-0.8350266372093458</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.0376</t>
+          <t>X &lt; 0.03767</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3418</v>
+        <v>3428</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.1193999955489318</v>
+        <v>-0.1263908946544277</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.3738169092499746</v>
+        <v>-0.3723586774846979</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.5778886775480885</v>
+        <v>-0.5760062528210526</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.5778330744234523</v>
+        <v>-0.5758746779689261</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.1955800661384259</v>
+        <v>-0.2057169908209957</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.4953741072035598</v>
+        <v>-0.4991012406262598</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.6519004157159287</v>
+        <v>-0.6604634418637545</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.518901757769747</v>
+        <v>-0.5281675478712629</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.6223647906415977</v>
+        <v>-0.6366310023966335</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.6540486366500033</v>
+        <v>-0.6578662158061377</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.9887099833909048</v>
+        <v>-0.9916181380425897</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.201327083954006</v>
+        <v>-1.208911045334162</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.137409718558416</v>
+        <v>-1.150613749038939</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.100230736563361</v>
+        <v>-1.118794262050841</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.04494</t>
+          <t>X &lt; 0.04499</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3557</v>
+        <v>3568</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.2120084675091363</v>
+        <v>-0.2062860778889402</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.4356157128388602</v>
+        <v>-0.4340710329478696</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.675214315528109</v>
+        <v>-0.673112397100212</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.8102508318240069</v>
+        <v>-0.8076738800606904</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.4922458258807438</v>
+        <v>-0.4991736587042368</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.5723184464302307</v>
+        <v>-0.5747250475085082</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.6699285684792926</v>
+        <v>-0.6762206104593531</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.5885794896505274</v>
+        <v>-0.5953387536188472</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.5780959630173115</v>
+        <v>-0.5890690575288673</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.7387049505617895</v>
+        <v>-0.7537296655329655</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.040225901267604</v>
+        <v>-1.054423692779693</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.215113070884435</v>
+        <v>-1.232920649175696</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.142004943371767</v>
+        <v>-1.164398567451542</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.12557243827878</v>
+        <v>-1.152086432569547</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.05227</t>
+          <t>X &lt; 0.05231</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3680</v>
+        <v>3691</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.3281946657902353</v>
+        <v>-0.3232867708913076</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.4626330011713193</v>
+        <v>-0.461098793920776</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.6803170195967922</v>
+        <v>-0.6782748724256109</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.7523123214044247</v>
+        <v>-0.7500096499015712</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.5441653507691981</v>
+        <v>-0.5490947007974825</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.6387786387677679</v>
+        <v>-0.6401109399408966</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.600364836046019</v>
+        <v>-0.6050575928387971</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.4830379536766358</v>
+        <v>-0.4882478850112477</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.5020482499721126</v>
+        <v>-0.5104445613980815</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.6585066020028876</v>
+        <v>-0.6699628246551157</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.8753169817558515</v>
+        <v>-0.8862064303681976</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.88021378105163</v>
+        <v>-0.8943059181492501</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.8506633702876201</v>
+        <v>-0.8682253386700438</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.9358516183401449</v>
+        <v>-0.9563157237918034</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.0596</t>
+          <t>X &lt; 0.05963</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3771</v>
+        <v>3784</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.3667511256717688</v>
+        <v>-0.3900170131935425</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.5631568420755784</v>
+        <v>-0.5896008173136522</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.6264821810131878</v>
+        <v>-0.6266843423628075</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.6671482325247027</v>
+        <v>-0.693463363205062</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.4240384469610845</v>
+        <v>-0.4567268254082535</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.5621047720571681</v>
+        <v>-0.5915389687273276</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.6060434375392845</v>
+        <v>-0.611577261194526</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.5027980143919564</v>
+        <v>-0.5090663051379494</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.5228250478011489</v>
+        <v>-0.5316311473115007</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.5370650361839893</v>
+        <v>-0.5490696972947262</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.7535512557033357</v>
+        <v>-0.7649841541200857</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.757468519794692</v>
+        <v>-0.7978369485004961</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.7122235357989197</v>
+        <v>-0.7556609164697434</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.7898720027382353</v>
+        <v>-0.8354357248457376</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.06694</t>
+          <t>X &lt; 0.06695</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3845</v>
+        <v>3856</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.4332229252984803</v>
+        <v>-0.4294708323824636</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.6049359322577601</v>
+        <v>-0.6031131085950534</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.6227656245357949</v>
+        <v>-0.6209808678429312</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.7639116591876842</v>
+        <v>-0.7616953661961503</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.587724632961752</v>
+        <v>-0.5902471080559764</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.6396090478413541</v>
+        <v>-0.6398590672675724</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.7622327106276643</v>
+        <v>-0.7642133839297358</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.6440195986271107</v>
+        <v>-0.6464443708318299</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.6129224503985498</v>
+        <v>-0.6175134184669275</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.6172716435594339</v>
+        <v>-0.624108954069591</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.8335520709982731</v>
+        <v>-0.8398231804176177</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.8627477702334403</v>
+        <v>-0.8709967194171711</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.8004836939889088</v>
+        <v>-0.8110766388486184</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.7942928463607259</v>
+        <v>-0.806925202269781</v>
       </c>
     </row>
     <row r="30">
@@ -5156,205 +5156,205 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3907</v>
+        <v>3918</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.4145894999221014</v>
+        <v>-0.4114092046885602</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.4304537439094815</v>
+        <v>-0.4291667726382542</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.5562966834425467</v>
+        <v>-0.5547286036260601</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.6676006241470347</v>
+        <v>-0.6656968286296276</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.5027009413539147</v>
+        <v>-0.5046553034169108</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.6256609508052833</v>
+        <v>-0.6255677630252165</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.6454832408488045</v>
+        <v>-0.6470014220045002</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.6131813783726727</v>
+        <v>-0.6148761647664074</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.6602227983123967</v>
+        <v>-0.663450808273808</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.7035575746347149</v>
+        <v>-0.7084742852821222</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.6894974320587224</v>
+        <v>-0.694493737604347</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.7176479449450639</v>
+        <v>-0.724217167783145</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.7397658097976034</v>
+        <v>-0.7480092732035075</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.781265646672793</v>
+        <v>-0.7910129004984086</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.08161</t>
+          <t>X &lt; 0.08159</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3972</v>
+        <v>3983</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.134617410710014</v>
+        <v>-0.1327344475096055</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.2768410794214731</v>
+        <v>-0.2760173205559795</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.4572475982352131</v>
+        <v>-0.4559803285027613</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.5394710669245768</v>
+        <v>-0.5379592858931801</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.4362591939218419</v>
+        <v>-0.4375743628242361</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.5523377575721966</v>
+        <v>-0.5520579951866509</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.5480696734780679</v>
+        <v>-0.5490495359198562</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.5239029717208084</v>
+        <v>-0.525013854831009</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.5962943714119149</v>
+        <v>-0.5984520904788226</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.577346459825165</v>
+        <v>-0.5809115677453889</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.6171462602528379</v>
+        <v>-0.6206315474061483</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.6442558283952096</v>
+        <v>-0.6489028513413828</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.7232070061431486</v>
+        <v>-0.7289357860935439</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.7351532515114769</v>
+        <v>-0.7420618775380134</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.08894</t>
+          <t>X &lt; 0.08892</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4009</v>
+        <v>4020</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.05513568503003796</v>
+        <v>0.05621597079861118</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.1005577316558757</v>
+        <v>-0.1002333544872798</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.2828934088507324</v>
+        <v>-0.2821149658345945</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.3133540129360526</v>
+        <v>-0.3124778447359162</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.2906571811756322</v>
+        <v>-0.2919119782387369</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.3779970472994094</v>
+        <v>-0.3779758933771404</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.3247045263760953</v>
+        <v>-0.3258443911981033</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.3050091428350328</v>
+        <v>-0.3062552891429746</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.4021536477015033</v>
+        <v>-0.4041486833630685</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.3662493263139197</v>
+        <v>-0.3694452265899173</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.4573677341957847</v>
+        <v>-0.4603389797953454</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.4589388270989545</v>
+        <v>-0.462911999271185</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.5409920175637453</v>
+        <v>-0.5457983619877709</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.5506991895657549</v>
+        <v>-0.5564658806207703</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.09627</t>
+          <t>X &lt; 0.09624</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4043</v>
+        <v>4054</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.1078413659153483</v>
+        <v>0.1085259916854255</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.03538202495452936</v>
+        <v>-0.03524660802610668</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.2441502720433988</v>
+        <v>-0.2434844629331891</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.149887940387849</v>
+        <v>-0.1494656917885351</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.1565371281270842</v>
+        <v>-0.1577382939352958</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.2406149867196703</v>
+        <v>-0.2407655142339991</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.237829803047191</v>
+        <v>-0.2387934722196121</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.1975029307943004</v>
+        <v>-0.1986174963723428</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.1955029134137973</v>
+        <v>-0.1974276325274857</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.1669895817144038</v>
+        <v>-0.1698664547654687</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.2837289865731094</v>
+        <v>-0.2863088421428017</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.3096768623968202</v>
+        <v>-0.3129846274297279</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.3450797211534393</v>
+        <v>-0.3491304983581429</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.3774925651187999</v>
+        <v>-0.3822383502901729</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4073</v>
+        <v>4084</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.08883433657283746</v>
+        <v>0.08935119683623327</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.04069453485889341</v>
+        <v>-0.0405545350428369</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2018588168742781</v>
+        <v>-0.2013126126432567</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.08283009388559748</v>
+        <v>-0.08259473794403505</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.09337005896785655</v>
+        <v>-0.09437636164230412</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.1501245351257268</v>
+        <v>-0.150341572139979</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.1724703259230083</v>
+        <v>-0.1732505909897029</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.1358591942938148</v>
+        <v>-0.1367701455105745</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.1097855676638275</v>
+        <v>-0.1113892879847711</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.0877150239200688</v>
+        <v>-0.09005503155659511</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.1560146785442953</v>
+        <v>-0.1581859754256172</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.2060269727352591</v>
+        <v>-0.2086812911711178</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.2196916846944035</v>
+        <v>-0.222958388129598</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.2010684759069434</v>
+        <v>-0.2049911290115247</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4089</v>
+        <v>4100</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.1031892839463922</v>
+        <v>0.1035521673328077</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.007732457663038872</v>
+        <v>-0.007685797202370281</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.194190581523948</v>
+        <v>-0.1936676183770061</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.09951247796320217</v>
+        <v>-0.09923531456378498</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.0877148822334135</v>
+        <v>-0.08854337312520499</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.1430850012349865</v>
+        <v>-0.1432267324404108</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.1412586224916339</v>
+        <v>-0.1419324004954703</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.08218782412330228</v>
+        <v>-0.08304710677067106</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.05644131550999276</v>
+        <v>-0.05789619624312792</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.03776644369123261</v>
+        <v>-0.03984388725748289</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.1065872311302059</v>
+        <v>-0.1084929741717033</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.1318134889994553</v>
+        <v>-0.1341739832738469</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.1470502216866976</v>
+        <v>-0.1499189139230879</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.1275988298407853</v>
+        <v>-0.1310320740438939</v>
       </c>
     </row>
   </sheetData>
